--- a/Results/2_parametrization/genetic_algorithm_run_iML1515iML1515final_run_1.xlsx
+++ b/Results/2_parametrization/genetic_algorithm_run_iML1515iML1515final_run_1.xlsx
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>146.5713881584375</v>
+        <v>291.2374572159707</v>
       </c>
     </row>
     <row r="3">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>32.70996287196558</v>
+        <v>81.37133126159945</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>62.74953453296263</v>
+        <v>96.05790266138568</v>
       </c>
     </row>
     <row r="5">
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>87.39822738608792</v>
+        <v>61.95360361399488</v>
       </c>
     </row>
     <row r="6">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>84.63270214502067</v>
+        <v>73.9089207415628</v>
       </c>
     </row>
     <row r="7">
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7.935080699368772</v>
+        <v>74.097785365391</v>
       </c>
     </row>
     <row r="8">
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>330.6878306878307</v>
+        <v>347.2016697834046</v>
       </c>
     </row>
     <row r="9">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>30.04957296681992</v>
+        <v>54.15726798036541</v>
       </c>
     </row>
     <row r="10">
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.005750184280706</v>
+        <v>0.9024303496134286</v>
       </c>
     </row>
     <row r="11">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.276449634618044</v>
+        <v>0.9024303496134286</v>
       </c>
     </row>
     <row r="12">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>20.0749437458249</v>
+        <v>19.0735590879787</v>
       </c>
     </row>
     <row r="13">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>19.33131118024431</v>
+        <v>35.61937131874576</v>
       </c>
     </row>
     <row r="14">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>28.47730927556741</v>
+        <v>5.202424815028913</v>
       </c>
     </row>
     <row r="15">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>12.98384992978067</v>
+        <v>16.91255500973224</v>
       </c>
     </row>
     <row r="16">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>7.736098772033571</v>
+        <v>33.73714294241403</v>
       </c>
     </row>
     <row r="17">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>14.22727098758386</v>
+        <v>26.68416205552244</v>
       </c>
     </row>
     <row r="18">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>7.671209521806778</v>
+        <v>3.539701963527189</v>
       </c>
     </row>
     <row r="19">
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>7.663998062541289</v>
+        <v>11.07198621322935</v>
       </c>
     </row>
     <row r="20">
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6.758583400919171</v>
+        <v>13.19124598053658</v>
       </c>
     </row>
     <row r="21">
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>11.91681836328804</v>
+        <v>5.928776545222211</v>
       </c>
     </row>
     <row r="22">
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>14.86069398828169</v>
+        <v>0.6456340315989516</v>
       </c>
     </row>
     <row r="23">
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6.245757649019942</v>
+        <v>6.758583400919171</v>
       </c>
     </row>
     <row r="24">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>386.5344889553066</v>
+        <v>141.5970080692576</v>
       </c>
     </row>
     <row r="25">
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>35.94971854462634</v>
+        <v>17.58746487517589</v>
       </c>
     </row>
     <row r="26">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>64.85003358916055</v>
+        <v>55.31496749064262</v>
       </c>
     </row>
     <row r="27">
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>20.62238161460763</v>
+        <v>3.431684374717887</v>
       </c>
     </row>
     <row r="28">
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3.270373802268027</v>
+        <v>7.888661404364036</v>
       </c>
     </row>
     <row r="29">
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4.13509345472191</v>
+        <v>3.646511640874274</v>
       </c>
     </row>
     <row r="30">
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>41.139114576167</v>
+        <v>9.180732016005397</v>
       </c>
     </row>
     <row r="31">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>22.18365121545629</v>
+        <v>24.52179224668194</v>
       </c>
     </row>
     <row r="32">
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>22.56814677600482</v>
+        <v>29.4625399863953</v>
       </c>
     </row>
     <row r="33">
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>15.77714350853576</v>
+        <v>2.715553724869807</v>
       </c>
     </row>
     <row r="34">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>271.214389550652</v>
+        <v>82.12121062485519</v>
       </c>
     </row>
     <row r="35">
@@ -1466,7 +1466,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>374.8388401603182</v>
+        <v>158.8488980852692</v>
       </c>
     </row>
     <row r="36">
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>34.76166970072938</v>
+        <v>12.77961940100785</v>
       </c>
     </row>
     <row r="37">
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.1460244871004775</v>
+        <v>12.48409878103913</v>
       </c>
     </row>
     <row r="38">
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>10.5263322135823</v>
+        <v>8.036900769243925</v>
       </c>
     </row>
     <row r="39">
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>182.6599676862326</v>
+        <v>274.1344332618728</v>
       </c>
     </row>
     <row r="40">
@@ -1591,7 +1591,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>50.98918616000964</v>
+        <v>137.7093307319506</v>
       </c>
     </row>
     <row r="41">
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>188.2123909386367</v>
+        <v>15.01639494216529</v>
       </c>
     </row>
     <row r="42">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>19.31745099870974</v>
+        <v>10.92414406022295</v>
       </c>
     </row>
     <row r="43">
@@ -1666,7 +1666,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>66.21572953757459</v>
+        <v>39.22668042739705</v>
       </c>
     </row>
     <row r="44">
@@ -1691,7 +1691,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>156.9631845651255</v>
+        <v>45.92430939023539</v>
       </c>
     </row>
     <row r="45">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6.758583400919171</v>
+        <v>12.34240968861915</v>
       </c>
     </row>
     <row r="46">
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.8018108942654916</v>
+        <v>0.3246938637062174</v>
       </c>
     </row>
     <row r="47">
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>258.744313134248</v>
+        <v>84.50871634678329</v>
       </c>
     </row>
     <row r="48">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>17.34744058016372</v>
+        <v>110.637359559667</v>
       </c>
     </row>
     <row r="49">
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>80.71672487326232</v>
+        <v>245.9087700047672</v>
       </c>
     </row>
     <row r="50">
@@ -1841,7 +1841,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>148.9573148370171</v>
+        <v>46.86973478237639</v>
       </c>
     </row>
     <row r="51">
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>172.6829403069612</v>
+        <v>38.00094126055599</v>
       </c>
     </row>
     <row r="52">
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>390.1248978813863</v>
+        <v>100.4394904802596</v>
       </c>
     </row>
     <row r="53">
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>179.6821910660003</v>
+        <v>36.75916250491174</v>
       </c>
     </row>
     <row r="54">
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>361.9458634644033</v>
+        <v>292.568066003213</v>
       </c>
     </row>
     <row r="55">
@@ -1966,7 +1966,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>50.34165038556694</v>
+        <v>0.4671032692063819</v>
       </c>
     </row>
     <row r="56">
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>118.0614570570395</v>
+        <v>84.01469248942257</v>
       </c>
     </row>
     <row r="57">
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>150.1239186311641</v>
+        <v>104.4542706169732</v>
       </c>
     </row>
     <row r="58">
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>225.9613392849828</v>
+        <v>182.3765857644132</v>
       </c>
     </row>
     <row r="59">
@@ -2066,7 +2066,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>338.9964212458448</v>
+        <v>22.59813859408348</v>
       </c>
     </row>
     <row r="60">
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>299.3116710893743</v>
+        <v>224.8401133144717</v>
       </c>
     </row>
     <row r="61">
@@ -2116,7 +2116,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>132.6925886748273</v>
+        <v>241.1899572101107</v>
       </c>
     </row>
     <row r="62">
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>22.31490260870747</v>
+        <v>149.1105748549722</v>
       </c>
     </row>
     <row r="63">
@@ -2166,7 +2166,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>92.57898109969274</v>
+        <v>44.44378878142754</v>
       </c>
     </row>
     <row r="64">
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>9.894318167387739</v>
+        <v>20.04537805268745</v>
       </c>
     </row>
     <row r="65">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.8820945717427211</v>
+        <v>0.008826656262615917</v>
       </c>
     </row>
     <row r="66">
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1.665583191856676</v>
+        <v>1.409274863278473</v>
       </c>
     </row>
     <row r="67">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3.02784003446508</v>
+        <v>13.0960183783199</v>
       </c>
     </row>
   </sheetData>
@@ -2302,11 +2302,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-3.873463070845681</v>
+        <v>-4.669098046462786</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>41.139114576166996,22.18365121545629,22.568146776004824,15.777143508535762,0.8018108942654916,6.7585834009191705,156.96318456512546,66.21572953757459,188.2123909386367,258.744313134248,50.98918616000964,182.65996768623262,10.526332213582297,0.14602448710047747,34.76166970072938,374.83884016031817,19.31745099870974,80.71672487326232,0.8820945717427211,9.89431816738774,92.57898109969274,22.31490260870747,132.69258867482728,299.31167108937433,338.9964212458448,148.95731483701712,150.12391863116414,179.6821910660003,17.34744058016372,271.214389550652,172.6829403069612,390.1248978813863,225.96133928498278,361.94586346440326,50.341650385566936,118.06145705703953,30.04957296681992,146.57138815843746,330.6878306878307,32.70996287196558,62.749534532962635,87.39822738608792,84.63270214502067,7.935080699368772,1.6655831918566764,3.02784003446508,1.0057501842807062,1.2764496346180436,14.860693988281689,7.663998062541289,6.7585834009191705,7.671209521806778,6.245757649019942,11.91681836328804,386.53448895530664,35.94971854462634,64.85003358916055,20.622381614607633,12.983849929780673,28.477309275567407,19.331311180244313,20.074943745824903,14.227270987583863,7.7360987720335705,4.13509345472191,3.2703738022680273</t>
+          <t>9.180732016005397,24.52179224668194,29.462539986395296,2.7155537248698067,0.32469386370621744,12.342409688619151,45.924309390235386,39.22668042739705,15.016394942165292,84.50871634678329,137.70933073195064,274.1344332618728,8.036900769243925,12.484098781039126,12.779619401007846,158.84889808526924,10.924144060222952,245.9087700047672,0.008826656262615917,20.04537805268745,44.44378878142754,149.11057485497216,241.1899572101107,224.8401133144717,22.598138594083483,46.86973478237639,104.45427061697319,36.759162504911735,110.637359559667,82.1212106248552,38.00094126055599,100.43949048025961,182.37658576441322,292.568066003213,0.4671032692063819,84.01469248942257,54.15726798036541,291.2374572159707,347.20166978340455,81.37133126159945,96.05790266138568,61.95360361399488,73.9089207415628,74.097785365391,1.4092748632784726,13.0960183783199,0.9024303496134286,0.9024303496134286,0.6456340315989516,11.071986213229353,13.191245980536584,3.539701963527189,6.7585834009191705,5.928776545222211,141.59700806925756,17.587464875175886,55.314967490642616,3.431684374717887,16.912555009732245,5.2024248150289125,35.619371318745756,19.073559087978698,26.68416205552244,33.73714294241403,3.6465116408742744,7.888661404364036</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -2315,11 +2315,11 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-4.043112753774289</v>
+        <v>-4.719892492815229</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>41.139114576166996,25.420066600574494,22.568146776004824,14.317632841559982,0.9348839552646018,6.7585834009191705,8.675695431748764,155.1569676959511,131.38381587159637,342.67668720368,50.98918616000964,182.37658576441322,10.526332213582297,0.12625729277925216,28.06987080774354,195.8888233130593,56.73171973377721,80.71672487326232,0.8820945717427211,6.7585834009191705,92.57898109969274,22.31490260870747,86.11233646813679,199.9791685748329,253.92811409234372,148.95731483701712,80.90064933627582,179.6821910660003,66.21572953757459,271.214389550652,172.6829403069612,390.1248978813863,182.37658576441322,273.37641745672454,33.92059290786593,134.76896990582912,30.04957296681992,146.57138815843746,330.6878306878307,32.70996287196558,62.749534532962635,87.39822738608792,84.63270214502067,7.935080699368772,2.3013334388701154,9.03532528149454,1.0057501842807062,1.321124927121248,7.596578225447472,7.663998062541289,6.7585834009191705,7.671209521806778,6.245757649019942,11.441791404815692,281.12800139592343,35.94971854462634,64.85003358916055,16.15227925406432,10.704840986010058,28.477309275567407,19.331311180244313,19.073559087978698,14.227270987583863,7.7360987720335705,4.13509345472191,12.897069767198998</t>
+          <t>24.809118641174802,45.78216022758797,22.568146776004824,24.255407500548177,11.136171283810416,10.94988802279714,55.812771901662565,130.2462617600637,46.89894777520771,223.62782635592004,48.39924342302681,354.56798323374346,6.7585834009191705,8.138007929389591,11.262284033237288,43.31592510903568,42.4697700177014,204.74860970967217,4.2623202046867785,10.335605055744553,12.533849908230781,505.1156329008741,44.849922811935805,70.69520891598323,195.34583976960107,36.747954200215865,99.02162000702762,275.6314791285956,57.27634900061284,343.5429459382562,2.8405694074260817,416.4640860697068,43.01450359942585,11.35035758605274,44.92387200649778,120.63807436421091,44.84337107351443,315.51453012329057,88.01045845131537,44.23470838303909,2.7163820332883803,32.44722737759192,84.41863003022884,107.00291130470463,2.160829291034198,11.193203901931001,0.9024303496134286,0.43499969488111073,4.929884228570731,14.958413270980516,1.6830506260644438,6.7585834009191705,2.542728865910718,2.035947340992194,131.7185123063304,33.58089166670025,69.07409265598756,3.431684374717887,12.05943206792191,24.10754632382966,20.321480444909508,19.073559087978698,16.221354676447707,0.7905641559716957,6.7585834009191705,6.7585834009191705</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -2328,11 +2328,11 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-4.077019286934247</v>
+        <v>-4.807678740843243</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>41.139114576166996,25.420066600574494,22.568146776004824,22.03523639599113,1.6549118058498,6.7585834009191705,8.675695431748764,155.1569676959511,66.9075121505496,172.6829403069612,50.98918616000964,182.37658576441322,6.7585834009191705,1.0439624712780842,43.816294052902045,139.2605605822254,42.4697700177014,100.40402579981847,5.898098507467123,6.7585834009191705,92.57898109969274,273.45715473299646,86.11233646813679,234.76823679663434,208.90802810730577,246.3224064713823,123.09570937595399,266.2236704789896,66.21572953757459,271.214389550652,172.6829403069612,390.1248978813863,182.37658576441322,273.37641745672454,33.92059290786593,84.01469248942257,44.91304997786726,188.81034378587395,330.6878306878307,32.70996287196558,34.944556965917876,87.39822738608792,84.63270214502067,74.097785365391,2.3013334388701154,6.7585834009191705,0.9024303496134286,1.321124927121248,7.596578225447472,7.663998062541289,6.7585834009191705,6.7585834009191705,6.7585834009191705,10.115668078543084,281.12800139592343,33.58089166670025,64.85003358916055,33.58089166670025,2.8044936485904457,15.230798380174132,15.280591927511557,25.253077341722808,14.859258362121578,6.777042917235754,4.891504517858715,6.7585834009191705</t>
+          <t>24.809118641174802,45.78216022758797,22.568146776004824,24.255407500548177,11.136171283810416,10.94988802279714,55.812771901662565,130.2462617600637,46.89894777520771,223.62782635592004,48.39924342302681,354.56798323374346,6.7585834009191705,8.138007929389591,11.262284033237288,43.31592510903568,42.4697700177014,204.74860970967217,4.2623202046867785,10.335605055744553,12.533849908230781,505.1156329008741,44.849922811935805,70.69520891598323,25.02115430502808,196.46788252107086,123.09570937595399,54.44163405917775,424.11547270563705,56.55262339459598,453.29473090296636,35.665393582612786,182.37658576441322,239.03180078010345,87.68136913946489,84.01469248942257,44.84337107351443,179.42460800523105,347.20166978340455,55.600618605499,52.39596207062338,32.44722737759192,84.41863003022884,107.00291130470463,2.160829291034198,11.193203901931001,0.9024303496134286,0.43499969488111073,4.929884228570731,14.958413270980516,1.6830506260644438,6.7585834009191705,2.542728865910718,2.035947340992194,131.7185123063304,33.58089166670025,69.07409265598756,3.431684374717887,12.05943206792191,24.10754632382966,20.321480444909508,19.073559087978698,16.221354676447707,0.7905641559716957,6.7585834009191705,6.7585834009191705</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -2341,11 +2341,11 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-4.420856047839238</v>
+        <v>-4.926274500848887</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35.25330351162232,15.552719376716581,22.568146776004824,32.11375909136936,10.030433241391549,6.7585834009191705,40.23100335884485,286.23012442997924,69.39642880541969,117.2297562321697,48.39924342302681,131.99450836057588,3.3815248528713955,6.530034469516218,43.816294052902045,94.65252955794274,83.08086052106502,101.3602816009449,6.7585834009191705,6.7585834009191705,87.50271656084925,273.45715473299646,100.40402579981847,322.79253572227526,106.08683844247548,246.3224064713823,149.62307393299318,266.2236704789896,176.27698725509674,425.0746203728048,172.6829403069612,62.65835628817881,195.49859095923722,187.3146523296262,50.278134273436756,128.8610439634523,1.8628999543045912,67.36286394800425,330.6878306878307,21.95504100702457,70.86239075293061,12.385688553707633,92.83487142405318,15.301096435025904,9.359244388057945,3.204343450739568,1.3000479715091129,1.1846234482868918,3.4946689649399003,8.44525059553626,13.044659084649393,6.7585834009191705,2.794529062832736,1.6398829151436713,210.5812885890211,33.58089166670025,69.48787507935415,21.981924949136197,19.642264001414386,0.6639520697185533,39.47846481989109,29.894010793135347,10.012283068868888,3.3742735709123157,0.9035376860608766,13.116344422303685</t>
+          <t>1.6353880924470472,25.420066600574494,25.608688746639718,22.9231990380021,7.470316122704257,0.4702203327834232,5.972299371306654,112.31736365144323,51.83778092541572,209.83159723537216,48.39924342302681,182.37658576441322,6.7585834009191705,6.7585834009191705,11.262284033237288,79.43802541479826,42.4697700177014,122.00358104273103,4.2623202046867785,6.7585834009191705,84.01469248942257,505.1156329008741,30.40141109013832,438.85185761568505,106.08683844247548,37.54137512996623,123.09570937595399,92.1174102840359,253.7993675764115,367.41794619167376,141.58640595754062,272.33115468409585,182.37658576441322,165.45714768643563,63.47410302257665,84.01469248942257,71.21115950704504,39.37003594395405,672.7681199951508,28.282046669902133,68.6986697560264,70.5736224028907,66.31649424338706,121.97931473345784,3.2135581304395866,6.7585834009191705,0.9024303496134286,0.3395142980885454,4.929884228570731,7.663998062541289,1.6830506260644438,6.7585834009191705,2.542728865910718,2.035947340992194,131.7185123063304,33.58089166670025,69.07409265598756,3.431684374717887,12.05943206792191,24.10754632382966,20.321480444909508,19.073559087978698,16.221354676447707,0.7905641559716957,6.7585834009191705,6.7585834009191705</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -2354,11 +2354,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-4.527916830806915</v>
+        <v>-4.932397913497547</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24.809118641174802,25.420066600574494,14.663897116713407,13.702235503131847,0.7356238413231273,6.7585834009191705,45.924309390235386,223.9482840567913,8.601358168914638,172.6829403069612,23.16533772397172,182.37658576441322,9.265174266680896,7.763821119126628,35.59169087329396,24.763392953230277,17.5603376574665,27.13302081725416,18.94111536757602,9.359244388057945,39.83259711018245,393.9444406513736,100.40402579981847,234.76823679663434,67.96201992543956,200.0860897936813,123.09570937595399,374.4796181358267,200.36691294926464,218.03445717083338,333.2932291303555,16.840438998514383,14.882462129817508,273.37641745672454,16.142279082727445,102.12002196932902,27.1179071325236,246.7354692461067,223.1909501884104,29.697438964990603,42.89993344700622,54.78552496409889,1.9280457690183903,74.097785365391,6.7585834009191705,11.13225328286807,0.9024303496134286,0.7068104255253372,0.07057866421903752,7.663998062541289,13.116344422303685,9.652517176718659,7.25850359516681,11.192293764493465,210.5812885890211,33.58089166670025,48.27471334889656,37.425589682973175,12.1503387958695,14.07512045656131,15.619005940052043,19.073559087978698,14.922860713204354,5.763719946688966,6.7585834009191705,12.317787210325907</t>
+          <t>1.6353880924470472,25.420066600574494,25.608688746639718,22.9231990380021,7.470316122704257,0.4702203327834232,5.972299371306654,112.31736365144323,51.83778092541572,209.83159723537216,48.39924342302681,182.37658576441322,4.2623202046867785,12.484098781039126,11.262284033237288,79.43802541479826,12.859453860804312,122.00358104273103,4.2623202046867785,12.633808222162502,84.01469248942257,376.4545776189341,30.40141109013832,438.85185761568505,106.08683844247548,21.59362246674353,107.55280388310864,92.1174102840359,273.28243382361376,367.41794619167376,110.30216459932073,330.42204224748264,182.37658576441322,165.45714768643563,63.47410302257665,84.01469248942257,71.21115950704504,39.37003594395405,672.7681199951508,28.282046669902133,68.6986697560264,70.5736224028907,66.31649424338706,5.155889133494859,6.7585834009191705,26.331781296890263,0.9024303496134286,1.4855752448970638,4.684820373112696,15.705404260543892,1.6830506260644438,6.7585834009191705,2.542728865910718,2.035947340992194,131.7185123063304,66.01779467324673,69.07409265598756,3.431684374717887,18.08194465994709,21.16299713972718,38.7873728022904,19.073559087978698,16.221354676447707,0.7905641559716957,6.7585834009191705,6.7585834009191705</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -2367,11 +2367,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-4.78103548086755</v>
+        <v>-4.941700003214792</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16.119992789896514,25.420066600574494,12.749077169166302,2.6400289794432967,6.991123807205158,6.7585834009191705,45.924309390235386,149.99610010139736,92.0937353821321,172.6829403069612,96.0447648730402,284.04717613960486,0.8173861290034279,6.7585834009191705,28.06987080774354,106.08683844247548,59.73947857427783,100.40402579981847,6.7585834009191705,6.7585834009191705,84.01469248942257,273.45715473299646,100.40402579981847,234.76823679663434,106.08683844247548,246.3224064713823,123.09570937595399,266.2236704789896,149.99610010139736,271.214389550652,172.6829403069612,272.33115468409585,182.37658576441322,273.37641745672454,44.92387200649778,84.01469248942257,44.84337107351443,188.81034378587395,330.6878306878307,28.282046669902133,34.944556965917876,70.5736224028907,44.22860883333776,74.097785365391,6.7585834009191705,6.7585834009191705,0.9024303496134286,0.9024303496134286,4.929884228570731,7.663998062541289,6.7585834009191705,6.7585834009191705,7.532377987800143,6.7585834009191705,239.01653502104344,31.03285090181452,34.94719478867431,37.98321125750463,11.459970281064813,7.325955223007839,12.333181388538627,35.66219101430774,15.693481959883021,10.992854762432373,6.7585834009191705,6.7585834009191705</t>
+          <t>23.505803652187648,25.420066600574494,25.608688746639718,45.30718958122842,6.7585834009191705,0.4702203327834232,23.235431165903087,149.99610010139736,51.83778092541572,172.6829403069612,48.39924342302681,182.37658576441322,4.2623202046867785,12.484098781039126,11.262284033237288,79.43802541479826,12.859453860804312,122.00358104273103,4.2623202046867785,12.633808222162502,84.01469248942257,376.4545776189341,30.40141109013832,438.85185761568505,106.08683844247548,183.5801377869078,123.09570937595399,54.44163405917775,253.7993675764115,271.214389550652,233.9360067695588,272.33115468409585,257.6846045692983,165.45714768643563,63.47410302257665,84.01469248942257,44.84337107351443,179.42460800523105,347.20166978340455,55.600618605499,52.39596207062338,61.95360361399488,84.41863003022884,8.518812996765039,6.7585834009191705,18.636349571790625,0.9024303496134286,1.4855752448970638,4.929884228570731,14.958413270980516,1.6303994254477026,6.7585834009191705,6.7585834009191705,8.439723229292037,131.7185123063304,33.58089166670025,55.314967490642616,3.431684374717887,19.27967982669594,15.230798380174132,20.321480444909508,19.073559087978698,16.221354676447707,7.7360987720335705,6.7585834009191705,6.7585834009191705</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -2380,11 +2380,11 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-4.781035480867562</v>
+        <v>-5.011205992972211</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16.119992789896514,25.420066600574494,12.749077169166302,2.6400289794432967,6.991123807205158,6.7585834009191705,45.924309390235386,149.99610010139736,92.0937353821321,172.6829403069612,96.0447648730402,284.04717613960486,0.8173861290034279,6.7585834009191705,28.06987080774354,106.08683844247548,59.73947857427783,100.40402579981847,6.7585834009191705,6.7585834009191705,84.01469248942257,273.45715473299646,100.40402579981847,234.76823679663434,106.08683844247548,246.3224064713823,123.09570937595399,266.2236704789896,149.99610010139736,271.214389550652,172.6829403069612,272.33115468409585,182.37658576441322,273.37641745672454,44.92387200649778,84.01469248942257,44.84337107351443,188.81034378587395,330.6878306878307,28.282046669902133,34.944556965917876,70.5736224028907,44.22860883333776,74.097785365391,6.7585834009191705,6.7585834009191705,0.9024303496134286,0.9024303496134286,4.929884228570731,7.663998062541289,6.7585834009191705,6.7585834009191705,7.532377987800143,6.7585834009191705,239.01653502104344,31.03285090181452,34.94719478867431,37.98321125750463,11.459970281064813,7.325955223007839,12.333181388538627,35.66219101430774,15.693481959883021,10.992854762432373,6.7585834009191705,6.7585834009191705</t>
+          <t>42.87319408525826,75.91466713154222,20.619269267637463,28.31106544763118,4.113718371674152,24.328596140738114,52.04949803851795,170.0019406208649,84.09080372487385,172.6829403069612,90.4137700678956,182.37658576441322,12.118282758687485,6.7585834009191705,81.85244345868402,106.08683844247548,42.4697700177014,101.96836736106637,0.45498780184301924,6.7585834009191705,132.31995438058453,539.9257819193649,6.7591985309578835,234.76823679663434,106.08683844247548,651.0620815660508,299.18622693415927,320.5598293060303,30.409390488507235,407.462092322603,38.00094126055599,100.43949048025961,182.37658576441322,490.99300403833905,0.714320534996684,84.01469248942257,8.079528094341278,429.6503684435167,55.931162544630695,19.1918683353547,96.05790266138568,66.3028880102485,123.50667835306578,74.097785365391,1.4092748632784726,13.0960183783199,0.9024303496134286,0.18817144542402883,0.6456340315989516,21.454042412680185,13.191245980536584,3.539701963527189,0.8851265560648433,8.565155110210368,276.3657489667987,17.587464875175886,57.87767256329671,43.02522076711055,6.772874593521949,15.230798380174132,21.662036631854583,9.955876853535026,8.734854729309959,4.9285602738116765,11.193203901931001,7.66914804304478</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2393,11 +2393,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-4.78103548086758</v>
+        <v>-5.011205992972223</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16.119992789896514,25.420066600574494,12.749077169166302,2.6400289794432967,6.991123807205158,6.7585834009191705,45.924309390235386,149.99610010139736,92.0937353821321,172.6829403069612,96.0447648730402,284.04717613960486,0.8173861290034279,6.7585834009191705,28.06987080774354,106.08683844247548,59.73947857427783,100.40402579981847,6.7585834009191705,6.7585834009191705,84.01469248942257,273.45715473299646,100.40402579981847,234.76823679663434,106.08683844247548,246.3224064713823,123.09570937595399,266.2236704789896,149.99610010139736,271.214389550652,172.6829403069612,272.33115468409585,182.37658576441322,273.37641745672454,44.92387200649778,84.01469248942257,44.84337107351443,188.81034378587395,330.6878306878307,28.282046669902133,34.944556965917876,70.5736224028907,44.22860883333776,74.097785365391,6.7585834009191705,6.7585834009191705,0.9024303496134286,0.9024303496134286,4.929884228570731,7.663998062541289,6.7585834009191705,6.7585834009191705,7.532377987800143,6.7585834009191705,239.01653502104344,31.03285090181452,34.94719478867431,37.98321125750463,11.459970281064813,7.325955223007839,12.333181388538627,35.66219101430774,15.693481959883021,10.992854762432373,6.7585834009191705,6.7585834009191705</t>
+          <t>42.87319408525826,75.91466713154222,20.619269267637463,28.31106544763118,4.113718371674152,24.328596140738114,52.04949803851795,170.0019406208649,84.09080372487385,172.6829403069612,90.4137700678956,182.37658576441322,12.118282758687485,6.7585834009191705,81.85244345868402,106.08683844247548,42.4697700177014,101.96836736106637,0.45498780184301924,6.7585834009191705,132.31995438058453,539.9257819193649,6.7591985309578835,234.76823679663434,106.08683844247548,651.0620815660508,299.18622693415927,320.5598293060303,30.409390488507235,407.462092322603,38.00094126055599,100.43949048025961,182.37658576441322,490.99300403833905,0.714320534996684,84.01469248942257,8.079528094341278,429.6503684435167,55.931162544630695,19.1918683353547,96.05790266138568,66.3028880102485,123.50667835306578,74.097785365391,1.4092748632784726,13.0960183783199,0.9024303496134286,0.18817144542402883,0.6456340315989516,21.454042412680185,13.191245980536584,3.539701963527189,0.8851265560648433,8.565155110210368,276.3657489667987,17.587464875175886,57.87767256329671,43.02522076711055,6.772874593521949,15.230798380174132,21.662036631854583,9.955876853535026,8.734854729309959,4.9285602738116765,11.193203901931001,7.66914804304478</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2406,11 +2406,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-4.781035480867607</v>
+        <v>-5.01120599297224</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16.119992789896514,25.420066600574494,12.749077169166302,2.6400289794432967,6.991123807205158,6.7585834009191705,45.924309390235386,149.99610010139736,92.0937353821321,172.6829403069612,96.0447648730402,284.04717613960486,0.8173861290034279,6.7585834009191705,28.06987080774354,106.08683844247548,59.73947857427783,100.40402579981847,6.7585834009191705,6.7585834009191705,84.01469248942257,273.45715473299646,100.40402579981847,234.76823679663434,106.08683844247548,246.3224064713823,123.09570937595399,266.2236704789896,149.99610010139736,271.214389550652,172.6829403069612,272.33115468409585,182.37658576441322,273.37641745672454,44.92387200649778,84.01469248942257,44.84337107351443,188.81034378587395,330.6878306878307,28.282046669902133,34.944556965917876,70.5736224028907,44.22860883333776,74.097785365391,6.7585834009191705,6.7585834009191705,0.9024303496134286,0.9024303496134286,4.929884228570731,7.663998062541289,6.7585834009191705,6.7585834009191705,6.7585834009191705,6.7585834009191705,239.01653502104344,31.03285090181452,34.94719478867431,37.98321125750463,11.459970281064813,7.325955223007839,12.333181388538627,35.66219101430774,15.693481959883021,10.992854762432373,6.7585834009191705,6.7585834009191705</t>
+          <t>42.87319408525826,75.91466713154222,20.619269267637463,28.31106544763118,4.113718371674152,24.328596140738114,52.04949803851795,170.0019406208649,84.09080372487385,172.6829403069612,90.4137700678956,182.37658576441322,12.118282758687485,6.7585834009191705,81.85244345868402,106.08683844247548,42.4697700177014,101.96836736106637,0.45498780184301924,6.7585834009191705,132.31995438058453,539.9257819193649,6.7591985309578835,234.76823679663434,106.08683844247548,651.0620815660508,299.18622693415927,320.5598293060303,30.409390488507235,407.462092322603,38.00094126055599,100.43949048025961,182.37658576441322,490.99300403833905,0.714320534996684,84.01469248942257,8.079528094341278,429.6503684435167,55.931162544630695,19.1918683353547,96.05790266138568,66.3028880102485,123.50667835306578,74.097785365391,1.4092748632784726,13.0960183783199,0.9024303496134286,0.18817144542402883,0.6456340315989516,21.454042412680185,13.191245980536584,3.539701963527189,0.8851265560648433,8.565155110210368,276.3657489667987,17.587464875175886,57.87767256329671,43.02522076711055,6.772874593521949,15.230798380174132,21.662036631854583,9.955876853535026,8.734854729309959,4.9285602738116765,11.193203901931001,7.66914804304478</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2419,11 +2419,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-4.79314724208921</v>
+        <v>-5.554320441048052</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16.119992789896514,25.420066600574494,12.749077169166302,2.6400289794432967,6.991123807205158,6.7585834009191705,45.924309390235386,149.99610010139736,92.0937353821321,172.6829403069612,96.0447648730402,284.04717613960486,0.8173861290034279,6.7585834009191705,28.06987080774354,106.08683844247548,59.73947857427783,100.40402579981847,6.7585834009191705,6.7585834009191705,101.98771583378617,273.45715473299646,100.40402579981847,371.0792461438465,106.08683844247548,295.9562356420613,123.09570937595399,266.2236704789896,211.17543159708532,509.80776685649283,325.35940928281923,245.82433813168643,182.37658576441322,273.37641745672454,44.92387200649778,125.57407714946986,44.84337107351443,181.48397188037686,641.4516829066745,28.282046669902133,34.944556965917876,70.5736224028907,44.22860883333776,74.097785365391,6.7585834009191705,6.7585834009191705,0.9024303496134286,0.9024303496134286,4.929884228570731,7.663998062541289,6.7585834009191705,6.7585834009191705,7.532377987800143,6.7585834009191705,239.01653502104344,31.03285090181452,34.94719478867431,37.98321125750463,11.459970281064813,7.325955223007839,12.333181388538627,35.66219101430774,15.693481959883021,10.992854762432373,6.7585834009191705,6.7585834009191705</t>
+          <t>17.389174675184137,4.9063955774777,26.48855346002949,18.92334968531565,1.382077781185087,11.336835025172038,55.812771901662565,130.2462617600637,46.89894777520771,223.62782635592004,48.39924342302681,354.56798323374346,2.580780309348783,8.138007929389591,14.265755740991517,79.43802541479826,1.2892534299059368,122.00358104273103,4.2623202046867785,5.322818482050563,146.6139701727804,326.88717522778535,39.37042922801291,1052.9992210637038,106.08683844247548,100.4445711654097,123.09570937595399,54.44163405917775,150.6441088201207,271.214389550652,417.06545880958635,67.68415631495361,154.5141929661188,24.760979680039455,0.36949305938732846,68.682051554496,15.171690420442474,395.7726062583071,81.88939063656439,87.0837844638941,562.7628718343384,14.432012443431422,163.08722007994322,17.450292522873017,0.07488990408856595,1.7150981141680843,0.8100695501189892,0.31418175704823514,1.3650493795921412,20.298353764457097,9.795469462729097,0.4732257238485097,5.169457708419965,13.451420135540577,19.939645702442927,33.58089166670025,57.87767256329671,43.02522076711055,3.2813437396729683,17.82076007970865,62.40660588929557,9.955876853535026,18.77538344162498,8.045943045439513,28.55181945844303,3.2158823975417508</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2432,11 +2432,11 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-4.853126386208754</v>
+        <v>-6.003364172906589</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15.86484533359101,36.34214052692148,15.320901650504386,24.255407500548177,10.090750054617324,13.221378985987304,42.67560099878069,206.23582713245645,46.89894777520771,220.47250653164585,59.26230254329684,221.39188816311938,6.7585834009191705,6.7585834009191705,43.816294052902045,27.79302046614106,42.4697700177014,100.40402579981847,6.7585834009191705,6.7585834009191705,104.09270661009509,273.45715473299646,132.93327256060874,348.42022162034516,106.08683844247548,246.3224064713823,123.09570937595399,266.2236704789896,131.40085691252713,271.214389550652,124.97876145965007,91.26126034149975,182.37658576441322,264.1318932163335,44.92387200649778,164.35250168589604,30.266111029036672,324.12758763932663,14.45158423912577,41.749971374458404,91.52729721561033,40.59357712860112,47.24981040146311,79.92496037846938,10.59273543031209,1.2179580860554593,0.9214389793747422,0.9024303496134286,5.853591988159366,16.094491571751337,8.90584614047615,6.7585834009191705,6.7585834009191705,8.304244844053969,80.81489324721875,61.202511435630825,34.94719478867431,6.0515815395349755,11.436075434177653,17.53430830775565,20.42389373082748,26.347482339664527,8.606200576779365,12.828196694865065,6.139949738544274,1.6549118058498</t>
+          <t>42.87319408525826,25.420066600574494,22.568146776004824,22.087453753035252,12.953658584125526,11.726112147272802,45.924309390235386,180.4172861299534,23.15001315007426,330.9681510677352,104.76583662285518,153.80584123355416,9.063702493743007,3.336136566583331,81.85244345868402,109.83573377741241,37.10724661997721,4.245129634960418,4.435001074318475,27.165038374638538,84.01469248942257,531.6425430826094,145.60656180637156,33.44683562043491,27.58766110688072,272.38989471817723,256.8830396197169,68.40576367332817,260.8465823177948,691.8669935886252,73.53350486178549,511.95453517620047,138.4715366811512,434.9009687256463,53.62025568201951,92.44098667432446,70.41194768083115,87.30716324463809,68.95380581041096,82.7753223714027,7.958558548987063,70.5736224028907,119.94573605394311,270.21471289537845,0.3255534961953752,7.452826714492409,0.7843380680877265,1.6940455249024926,1.2063130800004742,11.071986213229353,4.881483137555746,5.251983359540708,6.7585834009191705,4.406717420513752,141.59700806925756,7.202682492570821,57.87767256329671,43.02522076711055,1.7288752706917805,15.230798380174132,39.77685154404924,2.0850120946706783,3.1882242796977875,7.329692819782498,6.7585834009191705,6.000288793351045</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -2445,11 +2445,11 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-4.853126386208777</v>
+        <v>-6.3177867125755</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15.86484533359101,36.34214052692148,15.320901650504386,24.255407500548177,10.090750054617324,13.221378985987304,42.67560099878069,206.23582713245645,46.89894777520771,220.47250653164585,59.26230254329684,221.39188816311938,11.243605586920193,1.713807437951852,43.816294052902045,127.46327793062652,66.14565238330309,12.14290822744194,0.8900074955439067,13.384452743650984,84.01469248942257,308.8122947381376,216.80270160365524,467.7434254093612,146.90839610035954,246.3224064713823,123.09570937595399,126.2205442068202,282.6141507491457,352.6841676092724,172.6829403069612,407.04467772479614,175.29986174933387,165.317551364732,57.27063637886884,84.01469248942257,30.266111029036672,324.12758763932663,14.45158423912577,41.749971374458404,91.52729721561033,40.59357712860112,47.24981040146311,79.92496037846938,10.59273543031209,1.2179580860554593,0.9214389793747422,0.9024303496134286,5.853591988159366,16.094491571751337,8.90584614047615,6.7585834009191705,6.7585834009191705,8.304244844053969,80.81489324721875,61.202511435630825,34.94719478867431,6.0515815395349755,11.436075434177653,17.53430830775565,20.42389373082748,26.347482339664527,8.606200576779365,12.828196694865065,6.139949738544274,1.6549118058498</t>
+          <t>26.41000528314367,4.784146385839009,50.553961630184446,51.35006941966825,1.338876163204955,1.7594353423943738,41.66161874249256,552.6564903042959,32.92970037665598,11.806137858078221,3.954996377327836,182.37658576441322,13.462658079332973,3.8875053954258116,132.51871785042246,41.1886047592809,44.67004700147301,13.140915986299055,7.929026468775817,5.358828114963549,175.77139743082063,87.07310509427444,31.84176004483261,346.3437031855027,26.134474774316573,2.2359841082049097,181.59792147881186,69.23091033377081,35.37739102126763,416.7808489258462,35.50565410515054,149.00406098930193,25.53151185108639,292.568066003213,80.09111358538928,34.89301648887374,44.84337107351443,315.51453012329057,31.776833720040194,195.48520442375846,0.019611618515110864,54.668603446610575,133.75400424675624,14.117214434716605,5.300927391448344,8.023931098717703,0.8691127015976078,0.28037947529547663,9.207126117665538,15.322162427638522,6.7585834009191705,13.56084049319578,42.67918740391483,2.5713723648926448,0.8548872337571174,50.10979837355765,34.94719478867431,28.305443465875282,38.3120468516971,50.61919057421116,47.16489655409354,3.3283411532899607,6.286068001131252,6.132096402169513,11.031012848937374,3.4586161268408278</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2458,11 +2458,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-4.853126386208806</v>
+        <v>-6.317786712575508</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15.86484533359101,36.34214052692148,15.320901650504386,24.255407500548177,10.090750054617324,13.221378985987304,42.67560099878069,206.23582713245645,46.89894777520771,220.47250653164585,59.26230254329684,221.39188816311938,11.243605586920193,1.713807437951852,43.816294052902045,127.46327793062652,66.14565238330309,12.14290822744194,0.8900074955439067,13.384452743650984,84.01469248942257,308.8122947381376,216.80270160365524,467.7434254093612,146.90839610035954,246.3224064713823,123.09570937595399,126.2205442068202,282.6141507491457,352.6841676092724,172.6829403069612,407.04467772479614,175.29986174933387,165.317551364732,57.27063637886884,84.01469248942257,30.266111029036672,324.12758763932663,14.45158423912577,41.749971374458404,91.52729721561033,40.59357712860112,47.24981040146311,79.92496037846938,10.59273543031209,1.2179580860554593,0.9214389793747422,0.9024303496134286,5.853591988159366,16.094491571751337,8.90584614047615,6.7585834009191705,6.7585834009191705,8.304244844053969,80.81489324721875,61.202511435630825,34.94719478867431,6.0515815395349755,11.436075434177653,17.53430830775565,20.42389373082748,26.347482339664527,8.606200576779365,12.828196694865065,6.139949738544274,1.6549118058498</t>
+          <t>26.41000528314367,4.784146385839009,50.553961630184446,51.35006941966825,1.338876163204955,1.7594353423943738,41.66161874249256,552.6564903042959,32.92970037665598,11.806137858078221,3.954996377327836,182.37658576441322,13.462658079332973,3.8875053954258116,132.51871785042246,41.1886047592809,44.67004700147301,13.140915986299055,7.929026468775817,5.358828114963549,175.77139743082063,87.07310509427444,31.84176004483261,346.3437031855027,26.134474774316573,2.2359841082049097,181.59792147881186,69.23091033377081,35.37739102126763,416.7808489258462,35.50565410515054,149.00406098930193,25.53151185108639,292.568066003213,80.09111358538928,20.880694262847506,44.84337107351443,315.51453012329057,68.95380581041096,46.42947039992031,7.958558548987063,70.5736224028907,119.94573605394311,14.117214434716605,5.300927391448344,8.023931098717703,0.8691127015976078,0.28037947529547663,9.207126117665538,15.322162427638522,6.7585834009191705,13.56084049319578,42.67918740391483,2.5713723648926448,0.8548872337571174,50.10979837355765,34.94719478867431,28.305443465875282,38.3120468516971,50.61919057421116,47.16489655409354,3.3283411532899607,6.286068001131252,6.132096402169513,11.031012848937374,3.4586161268408278</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2471,11 +2471,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-6.091883180614977</v>
+        <v>-6.775168358973645</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15.86484533359101,36.34214052692148,9.954921321991359,13.702235503131847,10.090750054617324,13.221378985987304,4.644936323967926,213.33171693468714,46.89894777520771,432.93373601644436,117.60171256929038,344.81257771862533,11.243605586920193,1.713807437951852,5.299162392270943,81.65632949067779,93.04281096146686,16.220668631477988,0.7154941206858325,2.0017219271557436,6.855844318399738,308.8122947381376,184.67585139736468,568.5430424544718,146.90839610035954,148.95731483701712,123.09570937595399,82.95434534377509,282.6141507491457,238.03692540300923,277.00276339652044,272.33774482192905,136.08334991286827,296.85880431632467,57.27063637886884,84.01469248942257,3.2411769432401294,433.31538775258053,16.106155469920832,41.749971374458404,91.52729721561033,46.075015564766424,43.664603545403466,79.92496037846938,11.981400364165312,1.3038739658084846,0.4432085919028644,0.9024303496134286,10.944570682307987,16.094491571751337,8.90584614047615,6.7585834009191705,10.593558526773888,8.304244844053969,80.81489324721875,86.96764856986711,21.38168723521047,6.0515815395349755,21.82289601064637,25.94553685860503,13.865226519310815,39.337512476629485,7.678602420760241,12.828196694865065,6.198427100476093,2.0089423645303084</t>
+          <t>43.57481008984285,23.897037108399367,22.444454773952426,24.255407500548177,10.55114691579316,10.94988802279714,55.812771901662565,130.2462617600637,53.21750908661978,417.71915496025844,3.367319303294597,354.56798323374346,6.7585834009191705,4.117429866264041,11.262284033237288,47.877437403209655,10.916181368240085,204.74860970967217,4.2623202046867785,7.739320627796387,15.230211745742826,505.1156329008741,44.849922811935805,70.69520891598323,195.34583976960107,36.747954200215865,62.44827157113572,509.13193024108165,57.27634900061284,343.5429459382562,0.8600981643645115,416.4640860697068,80.40693692893649,11.35035758605274,44.92387200649778,120.63807436421091,33.42104503782383,315.51453012329057,88.01045845131537,44.23470838303909,2.7163820332883803,32.44722737759192,17.26325895670325,107.00291130470463,3.6562091089990685,15.16359067734513,0.5461829993303907,0.43499969488111073,4.929884228570731,21.135129778643382,1.599386414851518,6.7585834009191705,2.6697072771452075,4.002536765765775,197.4990892439305,29.479247068349938,69.07409265598756,3.431684374717887,12.05943206792191,24.10754632382966,20.321480444909508,36.405479857510365,16.221354676447707,1.3014218106888635,3.2135581304395866,6.7585834009191705</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2484,11 +2484,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-6.175734588487341</v>
+        <v>-6.805784015815333</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>35.25330351162232,25.420066600574494,13.807833754921065,46.28539210211825,6.7585834009191705,10.000683897119721,31.176765842520282,149.99610010139736,46.89894777520771,257.8203576058509,48.39924342302681,162.7195741543676,6.822952678276747,6.7585834009191705,53.18978876604946,167.68292240963916,51.02740527375966,100.40402579981847,9.515225833932908,6.7585834009191705,84.01469248942257,514.0235428375861,100.40402579981847,442.33700623085105,95.7610849733884,368.1702325789591,118.31924994700454,266.2236704789896,290.95491853858556,465.58924715385416,172.6829403069612,272.33115468409585,182.37658576441322,273.37641745672454,14.685334143219007,84.01469248942257,44.84337107351443,188.81034378587395,488.1615402958549,38.17023192810354,34.944556965917876,70.5736224028907,22.857636731609524,74.097785365391,6.7585834009191705,6.7585834009191705,0.5190731997727623,0.9024303496134286,4.929884228570731,14.894060786403676,6.7585834009191705,10.59273543031209,1.2179580860554593,6.7585834009191705,210.5812885890211,33.58089166670025,34.94719478867431,33.58089166670025,10.704840986010058,15.230798380174132,12.333181388538627,19.073559087978698,10.73266737637785,7.7360987720335705,5.8094366652553235,6.7585834009191705</t>
+          <t>24.809118641174802,45.78216022758797,22.568146776004824,24.255407500548177,4.1896744479353085,2.6414841812349557,69.69572165752622,130.2462617600637,46.89894777520771,223.62782635592004,48.39924342302681,221.7821325718657,10.697591705580853,0.831635887748323,11.262284033237288,78.01303808162544,42.4697700177014,337.3659023781316,4.2623202046867785,16.745183316501972,15.232649445709463,438.60755644602665,44.849922811935805,70.69520891598323,32.40289017666175,369.33939339332306,70.8040732748386,54.44163405917775,370.563754747831,60.893920690060156,453.29473090296636,27.78494225376866,182.37658576441322,239.03180078010345,87.68136913946489,101.93584462766005,44.84337107351443,179.42460800523105,347.20166978340455,31.542148988904867,28.094624972433877,32.44722737759192,84.41863003022884,87.47493150244102,2.160829291034198,11.193203901931001,1.2263436676287405,0.43499969488111073,4.929884228570731,14.958413270980516,1.6830506260644438,6.7585834009191705,4.748838769030488,2.035947340992194,179.93667657965747,52.51139585910695,69.07409265598756,3.431684374717887,12.05943206792191,0.1774064250486515,20.321480444909508,23.03510699883788,16.221354676447707,0.7905641559716957,6.7585834009191705,6.7585834009191705</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2497,11 +2497,11 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-6.593095890607847</v>
+        <v>-7.004853523432987</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>24.809118641174802,28.2582006607538,33.394113627410576,16.466337112089224,6.7585834009191705,6.7585834009191705,62.839622680726485,149.99610010139736,29.425766773197992,201.6021425635028,48.86020160597532,221.39188816311938,6.520073499465089,6.7585834009191705,52.6452531600657,51.11938823203096,40.84185878402426,195.46221416219103,7.2601836529345425,8.594551289645272,84.01469248942257,222.39630223232683,90.63139770632552,449.1205744821289,13.840627500734044,158.46385452502778,274.86887349882676,304.2486053209648,165.73760446636297,354.4507536369641,247.43019892631705,272.33115468409585,68.07086085176742,71.24964940234592,66.31664222155128,84.01469248942257,120.30932490364953,188.81034378587395,170.90165177723048,16.26768477739841,34.944556965917876,70.5736224028907,129.3940953114266,100.13815064639437,18.00110713650346,4.787962664930429,0.058229307082543744,1.3969589073290123,4.237552234544849,12.708637455710834,6.7585834009191705,2.793518168319291,6.139949738544274,1.7161935045022199,281.12800139592343,59.92128280359042,112.55680316523623,33.58089166670025,2.8044936485904457,13.885508016496184,27.61376551087795,4.56503702315984,0.24171861659253105,8.896247730634403,4.891504517858715,6.7585834009191705</t>
+          <t>39.268261713321266,45.78216022758797,22.568146776004824,2.4786984142111463,20.056516218008266,26.383907477840935,55.812771901662565,211.01788600650565,56.997270277127114,223.62782635592004,48.39924342302681,307.8823671067553,8.752499305988641,15.298617125109239,11.262284033237288,24.915116464544237,37.10724661997721,204.74860970967217,4.2623202046867785,10.335605055744553,13.496018689132212,393.50774747845765,44.849922811935805,70.69520891598323,30.35841020263406,196.46788252107086,69.83201450653047,29.19151078316834,424.11547270563705,46.2317968493267,453.29473090296636,35.665393582612786,247.83782058276861,446.4193952386525,119.77886695392934,131.3761653228524,44.84337107351443,179.42460800523105,347.20166978340455,55.600618605499,52.39596207062338,0.23877778909873215,101.95224532935904,107.00291130470463,2.160829291034198,11.193203901931001,1.464801975926691,0.43499969488111073,7.214870134640714,14.958413270980516,3.0855490924046904,2.5713723648926448,2.542728865910718,1.7751965511857153,162.74915924677285,33.58089166670025,63.109183488910254,4.005483763818673,12.05943206792191,24.10754632382966,38.94862340110217,33.09254020344779,16.221354676447707,0.7905641559716957,8.129313191826299,6.7585834009191705</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2510,11 +2510,11 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-6.852040015595315</v>
+        <v>-7.047491176506354</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>24.809118641174802,8.655667292387253,33.03893899122842,37.3757459455472,6.7585834009191705,10.115668078543084,45.924309390235386,149.99610010139736,46.89894777520771,230.53334989516514,89.81243217525528,182.37658576441322,11.243605586920193,1.713807437951852,43.816294052902045,127.46327793062652,66.14565238330309,12.14290822744194,0.8900074955439067,13.384452743650984,84.01469248942257,308.8122947381376,216.80270160365524,467.7434254093612,146.90839610035954,246.3224064713823,123.09570937595399,126.2205442068202,282.6141507491457,352.6841676092724,172.6829403069612,407.04467772479614,175.29986174933387,165.317551364732,57.27063637886884,84.01469248942257,46.705125882270416,259.60313231824097,330.6878306878307,41.749971374458404,34.944556965917876,70.5736224028907,59.692153001871596,38.29422414982758,3.7972210260837413,12.136309609634392,0.032385376267611746,1.1656323820506183,4.929884228570731,16.709093583745684,7.03917838844613,6.7585834009191705,9.292655188968281,6.7585834009191705,305.16375552167995,33.58089166670025,34.94719478867431,24.30406988527341,3.587313692669016,14.715752180739912,12.333181388538627,19.073559087978698,19.586380919779188,7.7360987720335705,7.03917838844613,9.292655188968281</t>
+          <t>4.38127944001331,45.78216022758797,37.18571380233075,18.92334968531565,10.94988802279714,8.21384749694395,45.924309390235386,130.2462617600637,60.73506584209305,622.1860518843687,159.31901941622246,143.00673727325145,10.588145562121229,3.336136566583331,88.1358971710767,106.08683844247548,28.362617565015434,6.7591985309578835,6.585025124365607,9.827672453455465,104.73692574446905,44.35742032900656,258.96406358510916,133.18367472569022,86.98956425282024,2.2359841082049097,181.59792147881186,69.23091033377081,122.62188404051517,389.4411885084851,35.50565410515054,149.00406098930193,25.53151185108639,292.568066003213,80.09111358538928,34.89301648887374,44.84337107351443,315.51453012329057,31.776833720040194,195.48520442375846,0.026650903516553106,102.0999080855732,182.7173005675227,422.5424356398108,1.3098834994378654,8.796739408793202,0.4510223991775007,0.9024303496134286,0.004751193833546584,11.071986213229353,15.931046807156312,3.539701963527189,6.7585834009191705,5.928776545222211,229.83665974222205,49.145529823308465,106.10756282820103,43.02522076711055,2.576809595676117,13.280137561472303,21.662036631854583,9.955876853535026,12.30320381340317,6.696735509574655,6.7585834009191705,7.66914804304478</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2523,11 +2523,11 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-7.869042665305091</v>
+        <v>-7.140928088046442</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>24.809118641174802,8.309661551843158,22.568146776004824,35.805844627977,9.121570971490382,6.7585834009191705,45.924309390235386,77.51897375283417,26.976028563402043,172.6829403069612,48.39924342302681,354.42701475465043,10.59273543031209,1.2179580860554593,43.816294052902045,106.08683844247548,45.52547226401465,86.30371103231174,6.7585834009191705,6.7585834009191705,84.01469248942257,453.45364270871374,91.21374042296304,234.76823679663434,106.08683844247548,246.3224064713823,30.14130781725904,266.2236704789896,260.340366538962,271.214389550652,246.3549071966246,286.90415306680717,28.170742281878564,273.37641745672454,58.97172251524248,73.3181649145264,49.41461404008686,161.93474039746278,330.6878306878307,95.60809641608883,5.042749453664671,70.5736224028907,93.5308685371488,55.94889087900327,6.7585834009191705,6.769085079875938,1.043717365115723,1.5083004885280307,4.929884228570731,7.579112634935475,5.796554502986554,4.531825415764952,7.532377987800143,4.367843532515641,368.30637825934724,66.53756578777136,34.94719478867431,44.830806301014604,19.86452136451176,15.230798380174132,12.333181388538627,4.996961224193617,12.405040274547277,7.7360987720335705,6.7585834009191705,6.7585834009191705</t>
+          <t>43.57481008984285,23.897037108399367,22.568146776004824,24.255407500548177,11.07513590793465,10.374649805178352,93.43712833465968,317.55022679838254,2.255896482911869,168.03870618875075,4.945995152584616,201.58229442790676,4.2623202046867785,5.779198702274163,11.262284033237288,32.43504670509042,42.4697700177014,204.74860970967217,4.2623202046867785,12.559066421881173,12.533849908230781,318.55263745413595,44.849922811935805,70.69520891598323,25.02115430502808,362.90511002069866,123.09570937595399,54.44163405917775,128.4182455105871,56.55262339459598,847.3430538071015,26.580845656365554,182.37658576441322,239.03180078010345,17.9304755430271,84.01469248942257,75.8767675343466,243.06903877316657,210.1388206370203,55.600618605499,74.03161272378138,32.44722737759192,80.22219173908236,112.34640657747724,4.248046355507941,16.78311983369355,0.9024303496134286,0.38186786721846355,9.40961255082202,14.958413270980516,1.6830506260644438,6.7585834009191705,2.542728865910718,2.035947340992194,216.8341980749823,33.58089166670025,69.07409265598756,1.6316906323856792,12.05943206792191,24.10754632382966,7.645391328349098,19.073559087978698,3.913140635486854,0.9872102296603396,4.227491230736753,6.7585834009191705</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2536,11 +2536,11 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-8.875521809509614</v>
+        <v>-7.390464807067931</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18.233258892742672,27.213221398242467,12.749077169166302,2.6400289794432967,3.362703562326555,6.7585834009191705,85.86554224727553,149.99610010139736,144.34983159150798,172.6829403069612,96.0447648730402,284.04717613960486,1.1614907288211265,6.7585834009191705,17.173944918132424,106.08683844247548,59.73947857427783,100.40402579981847,6.7585834009191705,6.7585834009191705,84.01469248942257,273.45715473299646,191.59602668686423,347.38683922550734,106.08683844247548,167.22158896432404,183.7852642226233,266.2236704789896,149.99610010139736,271.214389550652,172.6829403069612,272.33115468409585,182.37658576441322,243.9112128673529,44.92387200649778,84.01469248942257,44.84337107351443,190.60858827975403,401.4309343586275,44.703153633016605,34.944556965917876,70.5736224028907,44.22860883333776,74.097785365391,6.7585834009191705,6.7585834009191705,1.0842695677860266,0.9024303496134286,4.929884228570731,10.789934521779642,6.7585834009191705,12.704260701080782,14.192079705436724,6.100749997428718,239.01653502104344,46.38381094834184,33.59114542749077,73.67792982477809,11.459970281064813,7.325955223007839,12.333181388538627,35.66219101430774,15.693481959883021,10.992854762432373,11.602348100607728,6.7585834009191705</t>
+          <t>64.44368235882335,82.8311558154464,17.606998900439688,18.92334968531565,29.096019113959418,10.8930941515326,104.91026519569593,170.0019406208649,4.487849888774891,34.23886077562775,91.82245878430537,12.31206261704897,11.765464578582142,0.3231547247108502,89.41367731861574,79.43802541479826,15.570892867559763,55.60125822664,0.28317001990885937,6.518179275670625,46.54736685268359,26.377534246565816,148.12183532461754,26.947664044313928,106.08683844247548,7.624189731230026,237.16636898378022,500.47309361675724,521.9464080898487,197.86157933160172,104.1251551831278,247.95071905920798,13.925691385741931,445.4177454879818,83.90089529204928,17.983800226975884,53.0792419502923,306.03794870790483,269.65140022100184,28.702004259168902,50.01374384293209,49.8241960083461,30.386016491213777,7.674727083661451,13.28692447098856,56.913375360416424,0.19689176322946314,4.169666414107233,1.1351220905672812,0.5384542737474481,4.578043989029921,3.539701963527189,13.257088047984467,5.928776545222211,26.32605315806683,33.58089166670025,68.47741444043406,45.5894317332653,8.094896761447458,15.230798380174132,21.662036631854583,15.75831787999777,9.957407524580933,3.2291839998656644,12.624501131925651,0.5369094215093145</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2549,11 +2549,11 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-9.087046673122218</v>
+        <v>-7.549883708359451</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>41.139114576166996,47.678188210560045,24.16012453521941,20.01828429459446,0.7960061898964004,3.0942196293740003,79.70841596295071,260.340366538962,149.61421464080837,172.6829403069612,50.98918616000964,259.1537903606004,4.3563707826792095,1.0439624712780842,12.915172874356385,206.06401713251313,42.4697700177014,68.161565052797,8.80602255026815,7.915767457263167,93.46071056256768,238.64131586621247,115.19009878800391,201.3509043887316,411.3852844370284,246.3224064713823,123.09570937595399,185.761280023643,79.5581625519325,388.5250886926519,243.11561716687947,294.57095422102566,182.65996768623262,273.37641745672454,73.74394574515354,196.03309335451223,44.91304997786726,361.29396806810917,298.5009820170478,28.282046669902133,34.944556965917876,70.5736224028907,44.22860883333776,74.097785365391,2.3013334388701154,9.89431816738774,1.3905768220938182,1.350680362907341,4.929884228570731,7.663998062541289,6.7585834009191705,9.022772424364058,7.532377987800143,12.54161780981613,55.1688611845529,33.58089166670025,43.29895148329336,44.46054617030914,15.887085577028321,13.342613289704902,8.926103134778673,6.391766096634034,12.340571549752635,21.983908974828115,4.891504517858715,6.7585834009191705</t>
+          <t>42.87319408525826,25.280743732758275,21.382558348126825,18.92334968531565,6.7585834009191705,14.550496312561478,85.78299053039446,170.0019406208649,5.85051679707882,172.6829403069612,90.4137700678956,182.37658576441322,6.7585834009191705,6.7585834009191705,43.816294052902045,106.08683844247548,42.4697700177014,51.590955038321,0.45498780184301924,6.7585834009191705,146.25430063204365,531.6425430826094,100.40402579981847,60.343454916422495,106.08683844247548,309.5417513812083,186.99612734272003,266.2236704789896,19.17777022234374,747.2536708846111,27.664508755900503,610.3381685412437,5.235847148194181,124.50912842634936,45.02784931942241,96.51895606539432,24.90816869207132,57.521933496401886,2.883548177098335,156.89733582297248,11.413609441819114,166.80625891340324,38.67211412668786,144.62233509391095,0.5652290933740395,8.37692203323078,2.127966038642687,1.5825951917109384,8.498166656328006,29.407243433634445,0.213522530218442,14.640102174755127,6.7585834009191705,14.460473350798187,251.40958876687117,33.58089166670025,57.87767256329671,70.82785159567219,6.772874593521949,15.230798380174132,10.299823174588504,9.955876853535026,3.7461973967718047,1.7681703773095834,8.439723229292037,7.66914804304478</t>
         </is>
       </c>
       <c r="C21" t="n">

--- a/Results/2_parametrization/genetic_algorithm_run_iML1515iML1515final_run_1.xlsx
+++ b/Results/2_parametrization/genetic_algorithm_run_iML1515iML1515final_run_1.xlsx
@@ -451,7 +451,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="4">
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="5">
@@ -589,7 +589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,7 +622,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P00509</t>
+          <t>P00370</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CE_PHETA1_P00509</t>
+          <t>CE_GLUDy_P00370</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -641,13 +641,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>104.8336708977536</v>
+        <v>16.43224540934291</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P00509</t>
+          <t>P00370</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CE_TYRTA_P00509</t>
+          <t>CE_GLUDy_P00370</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222.293356096173</v>
+        <v>17.20883749783813</v>
       </c>
     </row>
     <row r="4">
@@ -677,7 +677,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>132.6858265000133</v>
+        <v>282.22073386657</v>
       </c>
     </row>
     <row r="5">
@@ -702,12 +702,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>f</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CE_ASPTA_P00509</t>
+          <t>CE_TYRTA_P00509</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>566.4310313576219</v>
+        <v>166.8732805627454</v>
       </c>
     </row>
     <row r="6">
@@ -727,12 +727,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CE_ASPTA_P00509</t>
+          <t>CE_PHETA1_P00509</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>134.5301132205433</v>
+        <v>419.7534327310582</v>
       </c>
     </row>
     <row r="7">
@@ -752,12 +752,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>f</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CE_CYSTA_P00509</t>
+          <t>CE_PHETA1_P00509</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>84.8461400097064</v>
+        <v>133.3032789138585</v>
       </c>
     </row>
     <row r="8">
@@ -777,7 +777,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>992.063492063492</v>
+        <v>122.7710952275143</v>
       </c>
     </row>
     <row r="9">
@@ -802,12 +802,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>f</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CE_PHETA1_P00509</t>
+          <t>CE_CYSTA_P00509</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -816,23 +816,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>211.7208672086721</v>
+        <v>2930.615251995847</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P00944</t>
+          <t>P00509</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CE_XYLI1_P00944</t>
+          <t>CE_ASPTA_P00509</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -841,23 +841,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>10.91207486556324</v>
+        <v>1285.549370253954</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P00944</t>
+          <t>P00509</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>f</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CE_XYLI1_P00944</t>
+          <t>CE_ASPTA_P00509</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -866,13 +866,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6.33144934726556</v>
+        <v>201.2777315850229</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P00944</t>
+          <t>P00562</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CE_XYLI2_P00944</t>
+          <t>CE_ASPK_P00562</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -891,23 +891,23 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>12.49871888131467</v>
+        <v>79.12845422615591</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P00944</t>
+          <t>P00562</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>f</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CE_XYLI2_P00944</t>
+          <t>CE_HSDy_P00562</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -916,23 +916,23 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>12.49871888131467</v>
+        <v>82.43424565368159</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P06959_P0A9P0_P0AFG8</t>
+          <t>P00562</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CE_PDH_P06959_P0A9P0_P0AFG8</t>
+          <t>CE_HSDy_P00562</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -941,13 +941,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2.738604775075104</v>
+        <v>64.86467898044049</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P06959_P0A9P0_P0AFG8</t>
+          <t>P00562</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CE_PDH_P06959_P0A9P0_P0AFG8</t>
+          <t>CE_ASPK_P00562</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4.201306438250039</v>
+        <v>30.14738092981779</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P0A6A3</t>
+          <t>P00864</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CE_ACKr_P0A6A3</t>
+          <t>CE_PPC_P00864</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -991,13 +991,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>281.4079402064409</v>
+        <v>141.6534703707052</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P0A6A3</t>
+          <t>P00864</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CE_ACKr_P0A6A3</t>
+          <t>CE_PPC_P00864</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1016,23 +1016,23 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>20.32470752745868</v>
+        <v>231.4446126873188</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P0A6P9</t>
+          <t>P00944</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>f</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CE_ENO_P0A6P9</t>
+          <t>CE_XYLI1_P00944</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1041,23 +1041,23 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>23.20829631610071</v>
+        <v>3.976462126269725</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P0A6P9</t>
+          <t>P00944</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CE_ENO_P0A6P9</t>
+          <t>CE_XYLI2_P00944</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>30.03684920660667</v>
+        <v>8.925213775400392</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P0A754</t>
+          <t>P00944</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CE_NADH5_P0A754</t>
+          <t>CE_XYLI2_P00944</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1091,23 +1091,23 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>20.2757502027575</v>
+        <v>11.01264538022549</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P0A754</t>
+          <t>P00944</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CE_NADH9_P0A754</t>
+          <t>CE_XYLI1_P00944</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1116,13 +1116,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>20.2757502027575</v>
+        <v>19.22323107573053</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P0A754</t>
+          <t>P05793</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CE_NADH10_P0A754</t>
+          <t>CE_KARA1_P05793</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1141,23 +1141,23 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>20.2757502027575</v>
+        <v>64.48780384852213</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P0ABI8_P0ABJ1_P0ABJ3_P0ABJ6</t>
+          <t>P05793</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CE_CYTBO3_4pp_P0ABI8_P0ABJ1_P0ABJ3_P0ABJ6</t>
+          <t>CE_KARA1_P05793</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1166,13 +1166,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>20.2757502027575</v>
+        <v>389.5447877183598</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P0AEP1</t>
+          <t>P05793</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CE_GLCt2pp_P0AEP1</t>
+          <t>CE_KARA2_P05793</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1191,23 +1191,23 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>20.2757502027575</v>
+        <v>46.19460485809763</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P0AEP1</t>
+          <t>P05793</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CE_GALt2pp_P0AEP1</t>
+          <t>CE_KARA2_P05793</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1216,23 +1216,23 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>20.2757502027575</v>
+        <v>40.51234636482859</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>P0AGD3</t>
+          <t>P06959_P0A9P0_P0AFG8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CE_SPODM_P0AGD3</t>
+          <t>CE_PDH_P06959_P0A9P0_P0AFG8</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1241,23 +1241,23 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>20.2757502027575</v>
+        <v>4.964794780714698</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>P60844</t>
+          <t>P06959_P0A9P0_P0AFG8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>f</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CE_H2Otpp_P60844</t>
+          <t>CE_PDH_P06959_P0A9P0_P0AFG8</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1266,32 +1266,2207 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>20.2757502027575</v>
+        <v>1.446621716146165</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>P06989</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CE_PRATPP_P06989</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1400.189407986044</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>P06989</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CE_PRATPP_P06989</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>3215.210764793998</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>P06989</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CE_PRAMPC_P06989</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1514.32454091013</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>P06989</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CE_PRAMPC_P06989</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>41.2413168980069</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>P07001_P0AB67</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CE_THD2pp_P07001_P0AB67</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>13.62556062657776</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>P0A6A3</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CE_ACKr_P0A6A3</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>45.12846764676395</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>P0A6A3</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CE_ACKr_P0A6A3</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>500.422062983316</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>P0A6A8_P0AAI9</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CE_MCOATA_P0A6A8_P0AAI9</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>24.14170137196017</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>P0A6A8_P0AAI9</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CE_MCOATA_P0A6A8_P0AAI9</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>62.85161898670792</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>P0A6C5</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CE_ACGS_P0A6C5</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>150.5457427777363</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>P0A6C5</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CE_ACGS_P0A6C5</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>982.9169133764601</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>P0A6K1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CE_DAPE_P0A6K1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>543.638484380417</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>P0A6K1</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CE_DAPE_P0A6K1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>204.5936983383134</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>P0A6P9</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CE_ENO_P0A6P9</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>59.13849710917282</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>P0A6P9</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CE_ENO_P0A6P9</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>75.45494677573406</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>P0A754</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CE_NADH9_P0A754</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>40.08840076203515</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>P0A754</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CE_NADH10_P0A754</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>20.92015394188159</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>P0A754</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CE_NADH5_P0A754</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>12.88336173269051</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>P0A799</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CE_PGK_P0A799</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>8.463880147775463</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>P0A799</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CE_PGK_P0A799</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>3.296305699336918</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>P0A825</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CE_ALATA_D2_P0A825</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>78.25937363579052</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>P0A825</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CE_THFAT_P0A825</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>15.27956978871902</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>P0A825</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CE_GHMT2r_P0A825</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>162.0837121453677</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>P0A825</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CE_THFAT_P0A825</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>29.23008380386157</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>P0A825</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CE_ALATA_L2_P0A825</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>3.387634490715119</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>P0A825</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CE_THRA2_P0A825</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>10.8376026484078</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>P0A825</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CE_GHMT2r_P0A825</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>442.6916590498957</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>P0A9B2</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CE_GAPD_P0A9B2</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6.527133035717778</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>P0A9B2</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>CE_GAPD_P0A9B2</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>62.12941039861123</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>P0A9B2</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>CE_NADPHHR_P0A9B2</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>8.269817170668102</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>P0A9B2</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>CE_NADHHR_P0A9B2</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>50.10311291568187</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>P0A9B2</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>CE_NADPHHS_P0A9B2</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>28.0339058382703</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>P0A9B2</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>CE_NADHHS_P0A9B2</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>24.13696779747049</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>P0A9M8</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>CE_PTAr_P0A9M8</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>1.159576895053597</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>P0A9M8</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CE_PTA2_P0A9M8</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1.177419033941432</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>P0A9M8</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>CE_PTAr_P0A9M8</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>3.503362942393624</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>P0A9M8</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>CE_PTA2_P0A9M8</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>9.833116782815948</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>P0AB80</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>CE_VALTA_P0AB80</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1576.371545142272</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>P0AB80</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>CE_VALTA_P0AB80</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>2185.533641179269</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>P0AB80</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>CE_LEUTAi_P0AB80</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>481.4789681103225</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>P0AB80</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>CE_ILETA_P0AB80</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>3359.562127798436</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>P0AB80</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>CE_LEUTAi_P0AB80</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1157.920432743922</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>P0AB80</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>CE_ILETA_P0AB80</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>4509.926921343812</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>P0AB89</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>CE_ADSL1r_P0AB89</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>2263.350093855582</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>P0AB89</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>CE_ADSL2r_P0AB89</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>547.0224875674636</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>P0AB89</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>CE_ADSL2r_P0AB89</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6.015838925569525</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>P0AB89</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>CE_ADSL1r_P0AB89</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>34.93008495729516</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>P0ABI8_P0ABJ1_P0ABJ3_P0ABJ6</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>CE_CYTBO3_4pp_P0ABI8_P0ABJ1_P0ABJ3_P0ABJ6</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>11.22209406871568</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>P0AC98</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>CE_SUCCt2_2pp_P0AC98</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>19.59927508624035</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>P0AC98</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>CE_ACt2rpp_P0AC98</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>35.06000773436543</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>P0AC98</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>CE_ACt2rpp_P0AC98</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>37.59370904292378</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>P0AD61</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>CE_PYK_P0AD61</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6.5077400040727</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>P0AD61</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>CE_PYK_P0AD61</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>2.307356584958282</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>P0ADU2</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>CE_QMO3_P0ADU2</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>45.59689141237649</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>P0ADU2</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>CE_QMO2_P0ADU2</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>8.593458242931431</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>P0AEP1</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>CE_GALt2pp_P0AEP1</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>31.75373190598899</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>P0AEP1</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>CE_GLCt2pp_P0AEP1</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>11.53344499978659</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>P0AGB0</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>CE_PSP_L_P0AGB0</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>219.8734672938868</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>P0AGD3</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>CE_SPODM_P0AGD3</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>4.907561469965488</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>P13009</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>CE_METS_P13009</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>84.23165135444576</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>P13009</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>CE_METS_P13009</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>78.13695421265083</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>P15639</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>CE_IMPC_P15639</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>98.19178974658335</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>P15639</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>CE_AICART_P15639</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>392.6651094548158</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>P15639</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>CE_AICART_P15639</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>328.9561991332156</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>P15639</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>CE_IMPC_P15639</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>193.724703656773</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>P15640</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>CE_PRAGSr_P15640</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>38.41816403442141</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>P15640</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>CE_PRAGSr_P15640</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>3670.237876342124</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>P23721</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>CE_OHPBAT_P23721</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>792.8013461520684</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>P23721</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>CE_OHPBAT_P23721</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>156.3234861803428</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>P23721</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>CE_PSERT_P23721</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>138.3314803411007</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>P23721</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>CE_PSERT_P23721</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>106.196157051192</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>P25516</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>CE_ACONTb_P25516</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>41.7399709618112</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>P25516</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>CE_ACONTb_P25516</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>0.991252343717296</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>P25516</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>CE_ACONTa_P25516</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>3.320019709433667</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>P25516</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>CE_ACONTa_P25516</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>68.60723285151592</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>P26458_P26459</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>CE_CYTBDpp_P26458_P26459</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>17.52228719562406</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>P26458_P26459</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>CE_CYTBD2pp_P26458_P26459</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>25.74409806045239</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>P37306</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>CE_CBMKr_P37306</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>838.4208311251135</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>P37306</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>CE_CBMKr_P37306</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>305.0754344027234</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>P60757</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>CE_ATPPRT_P60757</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>502.8801421620969</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>P60757</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>CE_ATPPRT_P60757</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>1269.54310409245</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
           <t>P60844</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
         <is>
           <t>CE_H2Otpp_P60844</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>mutation</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>20.2757502027575</v>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>18.75548377715408</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>P60844</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>CE_H2Otpp_P60844</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>34.62957302184823</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>P62707</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>CE_PGM_P62707</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>0.8772996361538646</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>P62707</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>CE_PGM_P62707</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>1.04897843302103</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>P75804</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>CE_GLCDpp_P75804</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>15.06275723097235</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>P78055</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>CE_F6PA_P78055</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>7.780238482843121</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>P78055</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>CE_F6PA_P78055</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>12.50299995955562</v>
       </c>
     </row>
   </sheetData>
@@ -1327,262 +3502,262 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-7.228372068256498</v>
+        <v>-3.075484238002039</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30.03684920660667,23.208296316100707,10.91207486556324,6.33144934726556,12.498718881314668,12.498718881314668,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,104.83367089775363,211.7208672086721,992.063492063492,84.8461400097064,134.53011322054329,566.4310313576219,132.68582650001326,222.29335609617297,281.40794020644086,20.32470752745868,20.275750202757504,20.275750202757504,2.7386047750751037,4.201306438250039</t>
+          <t>75.45494677573406,59.13849710917282,547.0224875674636,6.0158389255695255,2263.3500938555817,34.93008495729516,2.3073565849582818,6.5077400040727,141.65347037070518,231.4446126873188,78.25937363579052,3.3876344907151195,442.69165904989575,162.0837121453677,29.23008380386157,15.279569788719016,10.837602648407803,9.833116782815948,1.1774190339414323,3.5033629423936237,1.1595768950535974,64.48780384852213,389.54478771835977,46.194604858097634,40.51234636482859,15.062757230972352,792.8013461520684,156.32348618034277,138.33148034110067,106.196157051192,193.724703656773,98.19178974658335,328.9561991332156,392.6651094548158,219.87346729388685,79.12845422615591,30.14738092981779,82.43424565368159,64.86467898044049,838.4208311251135,305.0754344027234,1514.3245409101303,41.2413168980069,3215.2107647939984,1400.1894079860435,16.432245409342908,17.208837497838125,982.9169133764601,150.54574277773628,68.60723285151592,3.320019709433667,0.991252343717296,41.739970961811196,62.85161898670792,24.141701371960174,78.13695421265083,84.23165135444576,543.638484380417,204.5936983383134,13.625560626577764,3670.237876342124,38.41816403442141,19.599275086240354,35.06000773436543,37.593709042923784,31.753731905988992,11.533444999786592,500.42206298331604,45.12846764676395,201.2777315850229,1285.5493702539538,2930.615251995847,122.77109522751427,133.30327891385852,419.7534327310582,166.8732805627454,282.22073386656996,20.920153941881594,12.883361732690506,40.08840076203515,34.62957302184823,18.755483777154076,4.907561469965488,11.222094068715677,3.976462126269725,19.223231075730535,11.01264538022549,8.925213775400392,1.4466217161461647,4.964794780714698,6.527133035717778,62.12941039861123,28.033905838270304,8.269817170668102,24.136967797470493,50.10311291568187,45.59689141237649,8.593458242931431,2185.533641179269,1576.3715451422718,481.4789681103225,1157.9204327439224,4509.926921343812,3359.5621277984355,0.8772996361538646,1.0489784330210303,7.780238482843121,12.50299995955562,17.52228719562406,25.74409806045239,3.2963056993369175,8.463880147775463,1269.54310409245,502.8801421620969</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-7.228372068256498</v>
+        <v>-3.202936411549948</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30.03684920660667,23.208296316100707,10.91207486556324,6.33144934726556,12.498718881314668,12.498718881314668,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,104.83367089775363,211.7208672086721,992.063492063492,84.8461400097064,134.53011322054329,566.4310313576219,132.68582650001326,222.29335609617297,281.40794020644086,20.32470752745868,20.275750202757504,20.275750202757504,2.7386047750751037,4.201306438250039</t>
+          <t>3.2852004457119177,11.340200421422521,2469.5182431852472,21.91832307602592,407.9337703249287,20.686771050617867,0.4185743838795012,2.4066004263910417,106.21507306904054,59.69709570108117,18.230858918647307,34.33670899587623,1389.9082656855473,235.03945521097347,29.18911162667591,35.43259708347456,35.994906859834344,7.782912003278745,0.8665267116195543,7.988108646738443,0.7779638847737964,397.20986737681466,595.528005327244,48.79030685068781,21.08195765704057,12.138999820997725,25.35499147777151,218.8576482545521,259.41258015973,316.5899292562125,51.29073611438399,41.397796186812705,444.73858124028504,305.16189657343557,517.1474266212757,382.8639558891859,157.91041052573325,44.314028841807826,91.75219409285083,703.884495626064,147.23205843938743,1117.3531410997102,33.93150558798318,8201.350298224916,2864.8422741720483,5.4782341794337235,57.84459005974476,421.05613410223543,62.55017435263341,6.094121670459847,5.673120917736981,3.6801396813240164,19.027397880313302,60.21829874205004,72.05106255768787,111.1343497910311,93.40319084390453,244.4487932214572,229.3373294465187,56.494272220150286,1252.3078089547435,28.283875008151846,7.118100360065808,15.30449289269719,11.810633345890956,61.48964897569684,11.467867749032175,470.83927729015863,136.22541298975995,462.7548742021964,2928.7770653756047,1060.432662679775,72.85226963723726,100.30227233499606,115.26293047452901,123.62308816663716,414.9881356024274,24.395563946766924,19.74736458679737,35.17046728610355,7.451322183367392,61.667939559294965,9.441118867631118,24.84349295465625,4.910574272537417,12.812774520535596,2.3552657147071208,7.634201772595765,4.698085338929284,3.967348044336296,7.369844724850186,26.27837157801989,55.11188542782262,35.014054446693635,111.89776143580606,12.724897351578484,91.79176239392082,8.720473899792676,1961.9305419931804,3381.1802876362085,314.8418227235354,3526.5016913138397,1162.5417218363852,3305.7656898163627,1.5714519289141553,0.44650837912124997,5.148716234118947,70.73092701986323,23.418823471091663,20.04483872950533,1.6058232691845296,14.343028580572575,667.2478314925297,186.81236849843017</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-7.228372068256498</v>
+        <v>-3.293153303999184</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30.03684920660667,23.208296316100707,10.91207486556324,6.33144934726556,12.498718881314668,12.498718881314668,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,104.83367089775363,211.7208672086721,992.063492063492,84.8461400097064,134.53011322054329,566.4310313576219,132.68582650001326,222.29335609617297,281.40794020644086,20.32470752745868,20.275750202757504,20.275750202757504,2.7386047750751037,4.201306438250039</t>
+          <t>24.573344197436036,21.85882550485847,313.1575033739801,6.514394449784689,144.8000960772771,52.80007464810735,5.351929101035125,1.6611514188644843,20.887389440262247,23.293477235427797,4.980741871818688,19.13906602448116,1333.4786430660083,1510.0131017899098,46.55988353246731,27.779047518465806,15.278015955129082,3.638870772484043,0.9772976888516055,3.336064945355611,0.3788119489463412,697.8746324180996,264.7757191695509,8.53870475936058,39.80593008600507,27.191192396831454,239.73320745614285,95.07115713923935,162.22491397436963,200.07572022757324,164.99874220952023,210.491570957585,550.5236533647305,775.7072406868936,352.0155970692874,129.6931978908245,54.68339057604241,35.04914054610798,31.21465942307707,217.73511192162985,162.4561190601974,1172.0022815782645,31.96807411155244,2825.110651256045,1274.8757204807262,21.251081525747146,2.8796899287317035,348.75984200542064,561.4475554164262,88.89490058021573,3.8748256581574174,1.8210111686069217,43.2670461318002,120.27107626340019,70.66561818323365,318.2259074223877,79.9268928309903,725.3222936270114,395.09857571351495,90.69366805999753,823.7812307278164,192.76321157004875,24.47719358044765,37.7640159811835,18.620442090999035,5.192013117890517,139.37587605245352,480.28323749727855,17.99181966053131,63.44770260633439,700.3777400525279,1515.7631775984055,236.35707450910297,257.6505690546736,459.49047930623664,64.60172794542184,579.936111873976,70.05361425202358,71.40442899645056,59.377623700397145,44.527436989243846,57.1763386328804,44.554686377775475,30.8174352421429,51.04329647937039,1.9688101280986432,8.769233637493919,6.637352783154945,4.057564923462635,4.798214617545057,20.474115633784052,21.566568328800848,95.64118518751371,23.999429981206664,14.218309935901047,6.195708581388183,28.30883326827758,38.008668783965355,1004.1121566278388,6867.592901522577,198.19478261392402,4481.089073548051,987.5016623583856,3966.955115832095,1.5838395051619933,1.3891275903156715,4.790100536560995,17.326903544089085,30.757436810521877,5.218948881262034,1.859089797386221,2.6112694846725235,2092.9150468699936,1903.6301226030698</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>27</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-7.228372069088715</v>
+        <v>-3.322278465572962</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.03684920660667,23.208296316100707,10.91207486556324,6.33144934726556,12.498718881314668,12.498718881314668,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,104.83367089775363,211.7208672086721,992.063492063492,84.8461400097064,134.53011322054329,566.4310313576219,132.68582650001326,222.29335609617297,281.40794020644086,20.32470752745868,20.275750202757504,20.275750202757504,2.7386047750751037,4.201306438250039</t>
+          <t>7.781052859163295,27.058689329980005,2050.6511992275327,29.14503339249148,249.89026971183,11.275230177014869,0.5912440459307884,2.6723105958044,90.44057863101227,34.09435743520306,9.143375448192012,19.307425404986347,705.192860877341,443.155200428031,16.152547303534412,20.183526985647497,94.64182595070938,4.406443300511748,1.5762768240862226,7.988108646738443,0.5823501479461723,344.07348413544025,608.8407767647128,29.546486994824512,24.025070185082527,35.73282239244199,25.35499147777151,144.73250472486637,306.90781213501873,197.25289806800944,38.04053326682529,40.335339774024504,266.51811072139145,484.90342593924436,285.77731275211204,208.1479643094352,128.21167048683532,90.70738041187883,67.32852212668722,715.2724703651052,147.23205843938743,807.3967836293482,19.10400924828772,6266.857881506282,1760.695790292415,12.510286175756823,80.19600917876717,421.05613410223543,36.535544030778325,10.025155016732931,10.055197473112498,6.28704263009749,56.47045919479775,108.19956860741092,60.98151768282863,133.1844991539472,105.45429884217478,290.7150134628515,268.00946618092615,56.494272220150286,1783.485088282484,75.09083447888663,6.356911344636174,10.424922268235214,17.588487711715388,31.962781391561773,8.654431027556667,642.6945649523574,71.73101445380394,234.36026317087087,1539.4445539789908,563.1401449090622,63.785110138186695,100.30227233499606,105.95947202955533,71.44112509857324,210.36274333535994,17.718411036218615,24.35635451521927,31.786014881106208,16.931686269337,49.9551485528941,6.043819185826042,27.25128671814884,6.169861334525631,7.9997288658868575,6.667339349040558,9.786290788224978,4.698085338929284,3.3111948868817738,7.269434493638165,26.27837157801989,55.11188542782262,32.40172576995995,69.02636920294668,31.079553781356477,78.88431073932524,14.905649801477164,1523.4872730731527,2115.6142867792755,293.20216519515213,1785.9594782599117,1545.2131939416774,2351.3328630216974,3.8783258888027135,0.8971128875020682,7.632312816109628,112.33231286891646,34.26371310354849,26.81563145620592,1.3618188356852143,7.650942025331841,1122.1702190998465,414.40415493282774</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>27</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-7.228372069088715</v>
+        <v>-3.381027268989748</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30.03684920660667,23.208296316100707,10.91207486556324,6.33144934726556,12.498718881314668,12.498718881314668,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,104.83367089775363,211.7208672086721,992.063492063492,84.8461400097064,134.53011322054329,566.4310313576219,132.68582650001326,222.29335609617297,281.40794020644086,20.32470752745868,20.275750202757504,20.275750202757504,2.7386047750751037,4.201306438250039</t>
+          <t>63.84488144776671,7.203625482626985,205.3962613074531,2.693492577422995,825.5597388677589,14.54984283090859,2.8567562523608636,2.2484569151270763,214.434395485794,46.6984966454367,8.251947333075801,4.551135987928818,1390.003715946045,1464.2587755978643,59.691341951957874,34.094625635906155,5.377781970937688,1.0350696673649782,0.3613442902700276,5.207833037606074,0.3881524888794526,687.3617293946947,466.6979569313962,19.648773216758396,45.98129730764093,20.552980340468906,533.9189798145677,517.2639047192874,75.26277578671562,62.43447958156719,413.49790052834817,74.53084563355554,407.34523841630505,333.23159954851445,323.066304891097,69.4368764481345,25.748652320447913,60.707465661492364,107.06960592848478,453.46570440416644,202.70103786853866,482.8017751370557,23.033867083954668,4485.09974639079,1492.4571087609145,21.1052364649111,7.286521979761266,222.8696024646263,191.39908442601202,159.4364106260173,14.206862573615075,0.7928369000151853,19.541752353902332,38.85338876927484,21.645975827246012,380.57427500009874,80.95198697059064,78.01583301025796,124.30321532714368,12.342465211285141,728.9909219569001,64.77774045677782,26.858521561399748,17.545267847353777,11.772168587519438,10.559885969503402,16.31655065215186,276.2658665112874,32.68579330154492,424.10092942590205,1627.9269297163453,1711.034334084695,176.39236350241603,164.6559385551427,459.8510863027926,112.59838154703326,117.18955238825754,22.0678575818499,5.706234253515422,144.1639535768323,8.900296974316863,11.80200544370836,4.101931304591903,23.669951847192245,2.2736819572137033,6.180990413461044,18.3810695892615,6.775238996963142,6.30804862298946,4.037228897031029,7.153155259792353,78.85076532470049,28.10567171609046,22.363683571236944,53.48491739107255,38.28154276694711,47.946916176827926,34.34408918433985,2448.015416267697,1072.1411034953367,1272.1493095512626,955.7003231662695,6866.744218519075,3048.653568722615,6.076861730173214,1.4038487655048741,46.01141378166798,33.145734917882805,59.12875176062173,9.077915715844437,5.082947425929626,6.726684559000697,517.923135605317,1621.838043320048</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-7.228372106978017</v>
+        <v>-3.389560659568201</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30.03684920660667,23.208296316100707,10.91207486556324,6.33144934726556,12.498718881314668,12.498718881314668,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,104.83367089775363,211.7208672086721,992.063492063492,84.8461400097064,134.53011322054329,566.4310313576219,132.68582650001326,222.29335609617297,281.40794020644086,20.32470752745868,20.275750202757504,20.275750202757504,2.7386047750751037,4.201306438250039</t>
+          <t>166.1352333992526,33.58386289084974,623.3471622075504,4.932766772042045,1068.1925869052802,34.45574045592891,4.7299922177027245,0.950857908811167,214.3627680622301,149.91277765457326,73.04008352208844,37.35955496794878,168.3558068415228,1653.8332365758758,12.220645859813926,9.879137883836295,11.458779078847186,5.167871231444005,1.0061289031464136,6.142510820920167,0.3009897123727382,255.25561104735098,272.96858429587644,12.199637741798611,23.170065903026234,112.02807537833793,599.8263539119184,933.4966201606701,357.43250274476446,77.11238290920443,145.42094695727332,207.05981333437376,154.57378154398276,101.78328985921762,135.258075546854,16.585626019636802,20.51738826725198,92.6858378077558,15.648025516747584,449.55740277166603,246.67924587255237,1295.8167152693313,25.786993750578464,679.953408939325,2122.546506246252,9.60138113418055,15.172184138978588,1258.7586598610665,422.7884164575963,16.22571303129227,5.075755092317011,8.148040085829567,49.301494460827044,69.1354654549312,58.500861857180865,265.64756444255204,77.62975139758937,291.39287724939277,781.8140696842735,8.210830648864915,2441.610145175886,393.65180031538097,18.35377044605663,19.955809115200672,10.659706026505487,28.70470614016992,20.515686486314447,265.36269358828457,25.861604315462355,328.04632476599323,674.4112051959888,2559.1353436392155,69.57501976338997,147.33362204977308,216.29950623782798,75.67172488572263,484.4926874201072,32.77105226252661,22.574677465659185,17.5960554280151,18.379492878788433,26.328829801047007,16.157374993095097,40.035884494057626,16.231896935742167,7.988695112142932,13.322276698474234,2.522246693684419,1.3060972868141305,2.7378794732829874,25.945452851726266,21.62104489329282,14.93438426717232,22.876462199356887,53.71824129193419,36.33590495569639,23.40698818461901,10.74858861656018,3238.6396513116715,2161.723897524387,872.6876751843504,2074.0483915310315,337.6807465507977,1989.377341275735,0.3801363870262742,4.29189804443576,12.155225456645319,26.48221150241899,37.99166329592474,5.004258816915681,4.330070451895969,1.7182484376787608,1195.9167131201311,1789.918519627446</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-7.228372106978017</v>
+        <v>-3.489302121736681</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30.03684920660667,23.208296316100707,10.91207486556324,6.33144934726556,12.498718881314668,12.498718881314668,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,104.83367089775363,211.7208672086721,992.063492063492,84.8461400097064,134.53011322054329,566.4310313576219,132.68582650001326,222.29335609617297,281.40794020644086,20.32470752745868,20.275750202757504,20.275750202757504,2.7386047750751037,4.201306438250039</t>
+          <t>16.540626975164074,62.79454305602727,355.48153931548353,14.195694763661596,719.4004575234097,81.83699455979601,9.778098316683316,0.7966854261877652,80.77729812780379,211.589523784109,63.774234598089606,23.901803809196043,257.9685150752281,757.5934160974917,6.41726828696555,23.241582569649356,34.55234577806951,2.756727273276393,3.1942174086273702,3.4613249735772165,0.6779922918670532,187.47640582124268,664.5816748734683,2.738503898556585,21.247123123249917,52.302054576299646,231.0386573881542,282.0046649323243,97.12035383528465,118.89329132688492,519.3200332992421,176.35877196058465,562.3546004474333,176.89595032510692,253.26443948312357,104.94120922801257,44.56131825787178,104.49045671013526,72.296593600205,408.2224838269267,243.02519999037125,1240.3434351301064,19.884319635907133,5310.354195279331,1005.2214039716225,17.05992826023128,2.4128644154201555,213.81713789720766,141.51472044801778,123.41416617680254,1.2416626930975707,11.0936359013394,14.730122927677304,67.49675791125813,25.51644889308067,55.74783424922684,160.22174432413019,322.0100518309645,124.6943060954521,45.30218796614007,4633.142583137333,24.700644953227766,51.31178135426399,47.93686644740661,51.088063840241155,6.798856585860698,69.38388302992485,302.59483576299556,45.975414099950726,565.6020501835925,839.3421882984566,1216.7683518922609,68.79057617211087,180.3102526352345,43.62481102407332,280.33363079400243,343.9392812605205,44.01031882853266,13.817117598847219,30.228257064339555,5.92354868970218,15.303730588835538,24.877798416239,7.9445261962583515,5.630149330302542,20.29323592508977,6.5759484177143275,29.964432167153056,0.5455805351333793,1.8115319334277566,10.301197392467525,51.57404968689312,50.05391239689096,17.827310744047963,27.66070867310695,17.753001704605765,69.19679419071444,16.455846719310603,2737.9730460462156,1642.15667589639,186.36198732614736,1711.8334252784357,2077.517062903761,2441.2795417543475,1.558479920471185,0.6216744672452025,16.10757421081943,102.92470803463469,8.925505858372663,7.805833573472235,10.219444350231896,28.51781306420822,776.9520179814313,2065.1079629160163</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>27</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-7.228372106978017</v>
+        <v>-3.577205492325692</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>30.03684920660667,23.208296316100707,10.91207486556324,6.33144934726556,12.498718881314668,12.498718881314668,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,104.83367089775363,211.7208672086721,992.063492063492,84.8461400097064,134.53011322054329,566.4310313576219,132.68582650001326,222.29335609617297,281.40794020644086,20.32470752745868,20.275750202757504,20.275750202757504,2.7386047750751037,4.201306438250039</t>
+          <t>137.94042464749577,82.57144025865033,616.5615792549058,8.638225173324985,1979.9961122367645,16.276743637347916,4.483031531467121,6.96590374493775,83.15324706889372,152.05201267811645,111.24810580805551,6.662868120328429,698.3380047826605,255.03839994377884,39.97058862260685,17.878265206866704,11.168382562623677,18.59514165121627,0.915019033550043,3.5033629423936237,1.1595768950535974,29.859285484193656,466.8542199373095,25.14581390371479,29.18565245115988,11.393734701592535,1306.8990229031847,221.52942664932138,203.83521079828114,106.196157051192,139.42459973264695,116.52387371018152,502.98286617362805,744.1185504033087,142.81444971422655,140.98378474951144,48.404589515705254,37.465607985618334,25.934214212038903,1600.371799790829,305.0754344027234,2281.8901193017264,66.41622663565875,5984.056038433706,1151.6408895308875,5.852347507127379,26.720818201018574,865.8895756108285,148.29168470186164,106.56969758676172,1.2021323953048084,0.8800503588027239,50.97874246414728,64.92353502306337,15.585618960872047,123.42480054937737,165.37444546884237,815.7897975901503,193.03284850181456,18.141435672031005,2034.6501685230382,26.000149379740346,9.366238929530281,62.53277268876719,58.18453377557863,29.61358068360841,12.760352560440294,500.42206298331604,23.099779511842343,121.3064392246552,569.9463210151828,2869.0843402692767,178.75881630053948,133.30327891385852,375.2228978932513,166.8732805627454,441.7364748638789,15.683313560708655,8.857532230461327,42.02569776913366,55.8496280198733,28.5175650627616,1.9073309629593624,19.33643149553563,3.976462126269725,21.38314410079122,5.605027215452218,6.1968031833297434,1.235531964230968,7.420386472859897,10.490081982047572,102.34168207410647,22.562184644671092,14.355482202127774,20.49498930312664,51.60004299937272,57.372995794192775,12.19450816087532,1944.7503879723213,2599.1408025450537,228.15555571993445,2163.7405550042145,4954.143738252918,1418.4243699929193,0.367673156016579,1.2632432946320282,5.851075151604327,20.410542274237653,32.14830542776687,18.22567188346578,2.9685511534453735,9.940135964978294,2222.890879398187,1002.686259215062</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>27</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-7.228372106978017</v>
+        <v>-3.582227884077525</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>30.03684920660667,23.208296316100707,10.91207486556324,6.33144934726556,12.498718881314668,12.498718881314668,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,104.83367089775363,211.7208672086721,992.063492063492,84.8461400097064,134.53011322054329,566.4310313576219,132.68582650001326,222.29335609617297,281.40794020644086,20.32470752745868,20.275750202757504,20.275750202757504,2.7386047750751037,4.201306438250039</t>
+          <t>132.86526494331298,22.65361943352662,352.04259085847076,31.753569470907006,664.131880668102,29.268920345891633,1.5863305864157577,0.5577352971748808,11.577158339634106,173.0241195968808,26.350174790262024,13.163474615055744,101.47856070093755,3149.380287926855,30.05120578703803,4.731521191780606,33.38089492016654,2.6855225516238317,2.523323014630306,1.0633226186265212,1.120441622205357,472.80723195226824,669.403336129396,19.653380257977563,11.367743689910538,84.69032027353424,269.0402593324043,709.8358477326926,161.65727025636897,135.0421002683277,203.5127431445609,106.88399067980382,405.97648317980264,263.5258002799095,83.70428745302604,55.066033628779174,52.74882250522642,51.106002763065675,124.31895626339283,398.57000171576897,151.25887451112789,837.6200872785334,54.07670594817468,6226.083359919684,2681.0237522685147,3.5137499256344245,80.4531965614878,1801.398708163723,74.41634142514317,3.0560276880407233,11.072561267115905,1.3598132167248407,73.61943905092224,117.63420965552024,26.36861591680514,156.86247078472746,117.67897970597576,720.706159388452,239.306104290459,33.29019164272744,1483.7016493097663,45.82047053667346,8.58489399498301,19.21565331864847,67.77027571477431,24.263034012591422,19.048663186290575,1073.911875579011,92.3787307957149,407.0472766587164,1430.1925090637183,526.0954408717654,141.92460293634073,141.53119190022846,218.8567670730402,26.313152628064266,403.47812652809665,20.75862579880837,25.558360737752118,19.328388682000174,20.614079652301232,30.63116519760115,12.554652197334097,44.31110450054746,1.8037701133172617,4.138669421855948,10.19396197248798,22.438254440224497,1.6066574221972427,8.756574590894527,7.118994324846419,30.525308222541376,26.412203157136165,28.16419398770523,45.554702881630575,18.19620975056153,28.00672297491158,39.57678304541314,1521.3321538212815,2352.712584818426,1172.6929115346907,3353.2546719649467,1560.564548651077,2545.7977785183216,11.71945828040441,4.344138669571178,31.954038621761825,95.43608400119405,19.516051645805693,5.024831706130098,9.754092488423426,20.80073072726731,1930.1650310719128,4368.419039388815</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>27</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-7.228372106978017</v>
+        <v>-3.5939093661256</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>30.03684920660667,23.208296316100707,10.91207486556324,6.33144934726556,12.498718881314668,12.498718881314668,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,104.83367089775363,211.7208672086721,992.063492063492,84.8461400097064,134.53011322054329,566.4310313576219,132.68582650001326,222.29335609617297,281.40794020644086,20.32470752745868,20.275750202757504,20.275750202757504,2.7386047750751037,4.201306438250039</t>
+          <t>30.908536009290867,62.79454305602727,390.49560509054965,5.9934951746088245,165.92921054041744,65.71266420804672,9.588136486146023,0.679053616908089,96.39566758390379,84.58862589078001,57.433106921587296,14.2880769166563,1105.0389597157455,1357.1022812680085,28.382150451900028,33.84810776265373,31.692933040794617,1.9998645343053063,2.9550229771145395,8.681558489479363,0.2578592409042303,288.887073011766,299.92382171406985,9.56064406890786,21.51122279915185,26.17630151880561,225.98681960657143,465.67614409738815,112.67990800568272,56.32014419960508,220.3853055170801,350.85630607891346,528.9542858406653,295.47692201217944,420.60482179247026,67.59391530413484,67.04964833791816,48.098751561372666,55.44178590345183,861.6201046342454,447.0165718784135,1527.6545441657308,9.714251583985996,7236.704942227245,989.2171029117355,23.609165672941195,4.285598971965161,279.81953329973635,230.25973924194454,54.04286471769477,0.8955990480100318,18.992706369688907,8.954191849628842,38.081526514989356,14.936131599993036,18.783913542596352,89.17115834066266,322.0100518309645,147.32918416034673,37.80191565617971,4103.676243179622,20.76962857434181,51.31178135426399,41.01986802832215,51.088063840241155,4.7739458268395545,26.134282416989322,302.59483576299556,51.48060023444671,830.3421679704406,563.6165542036823,2340.805636594084,91.15344814807655,132.0956386881428,82.84851320737832,553.5313550921437,654.340863549756,82.87453842997313,15.78124384734738,32.882359883798884,10.250221856333074,15.303730588835538,49.07708950243891,10.93840731267672,4.564747628144648,22.453981504198946,2.8939533571639444,36.99007700589723,0.8522575751670224,1.6514736089608184,8.198692344788292,82.60363330148982,17.681755432519815,17.827310744047963,21.57788234103652,21.270972866291878,70.15258602155092,17.78256865350597,4438.492973944048,672.3479778054548,216.8554824092886,1001.4993579450602,2675.404152868918,2441.2795417543475,2.4907666859236848,0.6216744672452025,16.10757421081943,110.52102108230915,17.62403452515628,5.872721795575858,14.367633367982462,11.555081659730778,386.7022657202362,1393.1104699261682</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>27</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-7.228372106978017</v>
+        <v>-3.692158257692007</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>30.03684920660667,23.208296316100707,10.91207486556324,6.33144934726556,12.498718881314668,12.498718881314668,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,104.83367089775363,211.7208672086721,992.063492063492,84.8461400097064,134.53011322054329,566.4310313576219,132.68582650001326,222.29335609617297,281.40794020644086,20.32470752745868,20.275750202757504,20.275750202757504,2.7386047750751037,4.201306438250039</t>
+          <t>6.571128277981001,26.886795320505147,226.66327044457893,26.89464059530812,1348.6419435635075,48.660672174754296,4.407942546440479,1.5421406543007423,83.1983376647083,232.00039977124771,85.44031631209921,28.188445271016114,317.6442245057405,351.5421313732043,5.476520909862376,15.330800390933259,44.39767910060288,4.183639204767245,2.09324751240396,1.8536528682415199,1.078082810543337,283.03487245272356,1134.2658929829192,1.8960458266926739,11.03114317470612,18.13904890617952,257.03693560031013,276.144522935684,123.94728984338332,198.58435044696995,418.58119003519505,346.4435903979729,391.23561707056103,299.48159349709096,325.2791100536075,111.5343150873673,47.91153859385702,92.66920269406202,83.99335292642871,227.98525836446092,152.05543669714712,1039.9244423499072,20.06389031791602,3946.8280195236025,1358.2087178311172,17.741081316875814,1.9445642041069535,119.92451674935413,51.410336322814715,133.3071524064423,4.632912711022924,6.8697874894750015,45.70385864240632,67.49675791125813,16.391450888877102,207.35151324257964,300.3009108137849,525.9157159512453,103.83690388882647,10.14512348295884,3348.99739660641,56.93141118023738,28.564127947833995,71.56748752787954,29.323094570404287,37.77228115349676,44.458763964977145,120.2102475428679,16.583712966752458,293.66672976070674,716.5056691264377,2019.1771952695362,68.79057617211087,239.85771892666344,61.02610242873641,281.502794962736,290.0308005989325,60.73809238757035,18.417552491268655,15.531982150211789,11.37450666222397,17.358418720658992,24.406838747622746,18.75410673690068,4.347483319377705,6.241213987776103,8.631419823176294,25.077487592501456,1.5677818783760977,2.7820636398062644,8.781551161341179,50.85147388849098,56.40941989192547,11.010156645962244,59.15144497011525,11.374831044475151,57.801914576991834,34.083790318756726,1555.9299033557136,944.9403453237599,396.9696204602993,2625.530534606169,1403.08516564157,3561.2201691748533,5.797822422469605,0.9165937156362005,15.46335709744562,64.39411994741191,11.899711731466372,11.589848365815437,10.030078938452759,17.93424395120511,757.5984961872356,4598.319704131671</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>27</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-7.228372106978017</v>
+        <v>-3.759622275136672</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>30.03684920660667,23.208296316100707,10.91207486556324,6.33144934726556,12.498718881314668,12.498718881314668,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,104.83367089775363,211.7208672086721,992.063492063492,84.8461400097064,134.53011322054329,566.4310313576219,132.68582650001326,222.29335609617297,281.40794020644086,20.32470752745868,20.275750202757504,20.275750202757504,2.7386047750751037,4.201306438250039</t>
+          <t>96.2764218795711,14.19807141659054,88.4714604228485,10.489491833236018,1449.2871150042645,6.484278978055107,5.045766168001936,3.408673762273403,166.8828535551952,30.771061514288398,12.592162976520568,8.498333708030342,480.54942374989866,1956.109137081442,45.64433005077022,19.53969916515257,12.826123645190593,1.749425556523427,0.35394926820157113,7.0785095077201445,0.33504668394515846,538.5903512371926,448.45816130329666,32.86874662975679,24.023554071358966,49.29748397301258,198.4715072175819,728.8142172420876,130.25371105566455,71.51968818598218,227.77870573247944,87.4231281915295,717.7656784684629,296.4340343351204,399.6721595240217,63.36423510595853,27.611671113150173,60.707465661492364,25.31362817733809,549.4365464804732,333.3854226596028,482.8017751370557,20.140980811137275,2680.7189910039097,590.905887560992,7.969945193227616,6.317764875207603,124.03772468292046,99.50064139552708,96.05918478604261,9.022884439580974,1.4513224518773336,42.02495021400004,36.34874838707666,15.199131598577338,143.34792388606837,63.495061757705265,140.14540800629217,182.48555016187444,4.799934151041481,1402.4247561081584,115.83569992400167,10.197633706689409,56.099798104630075,44.87105666817918,20.090071942198232,37.786211200649674,225.68449856625892,10.751357929262488,90.53201389456696,2560.125338172528,1371.3241686886831,98.79387616247996,349.4766312110304,202.21326730469502,136.73215517448955,979.3683005543609,38.022856812075055,30.70125127345272,61.15211127923233,11.855283373738986,31.03294279500747,53.383734242639854,34.720433465563126,30.89748544042406,7.221788279037403,5.662224297548307,6.400467586274869,1.9778698825005223,5.949123085909905,17.508068783051577,13.58007439647358,68.94644721382144,35.930576328742816,5.743774376213398,7.646407259481513,7.8412428275727635,27.897756134857943,442.8970876522609,2328.3453411657993,133.39610925693017,3323.1556507838814,897.3248973023052,1299.0069684463742,6.356630307065472,3.296636978944311,18.42618993974591,8.820702487657993,101.6539744723978,14.915875326596346,1.8963050503269216,8.794099727291876,1515.3668625842447,1828.9105171623423</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>27</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-7.228372106978017</v>
+        <v>-3.759700113139312</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>30.03684920660667,23.208296316100707,10.91207486556324,6.33144934726556,12.498718881314668,12.498718881314668,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,104.83367089775363,211.7208672086721,992.063492063492,84.8461400097064,134.53011322054329,566.4310313576219,132.68582650001326,222.29335609617297,281.40794020644086,20.32470752745868,20.275750202757504,20.275750202757504,2.7386047750751037,4.201306438250039</t>
+          <t>25.28235086252676,8.651128465823227,33.82278981724095,40.279399403429515,2674.0482564453096,8.464271474327505,1.8416966192239599,2.452359861147901,107.37209283905506,81.40669402677727,20.942948043409096,50.94559506697119,1255.1317310366326,759.6435406323423,27.717756578505746,7.562936193035462,47.799597137262026,5.624682158213101,3.6055592355001505,0.9269850400604123,1.0219504592142787,260.70817054547103,220.3455344844412,22.05806583637033,20.319986241743116,108.10920774013037,1164.4378322557434,304.8752159222258,166.02053774848156,137.16646924949487,87.05155350318253,158.82132675559834,148.19314342827082,143.85740936490026,93.06886549453044,13.604107214415222,16.71601344398313,118.4742039168865,20.66802151337215,181.31571869675741,111.19057674816275,514.1278411626769,18.513119450952463,481.3167846945238,1892.9899341259297,17.169948611965424,14.44276761793758,1246.3599798835535,142.98354309608072,69.27584210409535,4.966535069512282,3.8679419538618287,42.86327554479813,118.81643913460692,148.51002013964538,487.0450071273507,147.7887727486177,585.8794232326545,1371.804480370622,38.924707674010236,2335.1141647324807,69.55319927950256,3.1108629608754343,27.565574821842056,52.944348384161664,19.00338287096186,28.87298290568155,109.4588902955409,32.553090124797706,119.29995830132842,350.0649458435923,1204.462654056253,198.4317699728264,67.35264387176029,211.8772795646271,290.58887091407667,140.01126224129627,19.6022969118158,9.988943433075923,40.44681763191225,33.906022017857225,51.81450560084871,34.15169200904737,40.035884494057626,4.244436652625154,3.838255291669005,96.16432018146003,29.447186231677694,0.8131155378154683,2.4962488369738,21.680165766459123,26.58616379453635,98.71871974871371,50.58880250428518,76.74685859899252,103.01943921903981,29.801171326090333,76.91366227801979,1582.0906536595444,1633.470477935269,1639.5990323124718,6403.26849721489,2082.1521070612944,3081.0827568452937,1.2893747212856754,1.701635864543437,5.288390939534843,25.1794185054186,50.901730806975294,4.1523979086471625,2.301950210902974,11.989333546418262,2048.9207290620666,418.02353191854945</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>27</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-7.228372106978017</v>
+        <v>-3.85289898274882</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>30.03684920660667,23.208296316100707,10.91207486556324,6.33144934726556,12.498718881314668,12.498718881314668,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,104.83367089775363,211.7208672086721,992.063492063492,84.8461400097064,134.53011322054329,566.4310313576219,132.68582650001326,222.29335609617297,281.40794020644086,20.32470752745868,20.275750202757504,20.275750202757504,2.7386047750751037,4.201306438250039</t>
+          <t>290.8924430209773,66.96243305062393,1108.5729797302847,9.722295402466903,566.5450917514195,62.26463451543727,4.7299922177027245,1.6692506314926627,81.52809598828762,264.7845160102554,40.152327575775395,49.90877845363249,194.35553970591445,1653.8332365758758,11.953432047338246,9.879137883836295,18.921956694517572,4.534798093784064,0.341797757844571,9.288414342032434,0.3009897123727382,215.75376723519503,272.96858429587644,26.967379720501853,48.85764790727244,12.548143181295066,492.61265663372626,165.9438716235009,215.29831615409162,436.32734656742065,263.8266287598698,165.63923577933627,115.35267604428006,564.9476921766313,310.34133762914837,87.70982574416617,61.181588249514775,146.1096868321225,20.0842493096519,57.12298663740924,41.79677172432828,281.0947535238644,14.709986213568468,721.1142690459119,1203.6092741405155,4.945676280367572,8.33597367058327,177.67057806578907,188.5608697736972,65.6704164180825,12.075030185214512,4.062851881923514,176.34070545512523,122.20513461229685,34.92000926298575,126.79807082666596,16.88760358414983,352.36402808300136,577.8698810102212,17.111386012029318,4723.5251419369615,10.208035214061374,13.971220009726473,39.11949189248813,111.63110866125928,53.06017330461582,55.899421690906145,463.17982026622536,27.986019184011248,272.840548888575,2086.631622584816,2853.01459103186,58.95217247897611,226.55665622006626,71.99566982184848,335.8919671932473,657.8977930758276,20.493057443705347,15.793841835821105,56.478001344652405,9.250335708007679,18.648027251849626,29.694286889051064,85.30785569173716,10.510650737206843,27.379109592309653,10.958519434490674,21.710997612015127,1.5591119025534117,12.369962762442727,92.07901765086002,14.72602080924033,63.18970376478998,15.95258187009323,68.01516228811904,5.753165913182309,18.640190684916025,27.36796594595991,1391.8740670863226,1301.4296114194813,635.2162700713917,6654.013756488677,4053.789319453047,2116.3251620647898,1.0787846759015165,5.755354159680971,53.05052833986366,72.76869056852665,20.813617528248407,12.45341035168439,12.302344400533157,48.648287753950015,1151.9689225661477,1527.5232016713471</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-7.228372106978017</v>
+        <v>-3.902871646724675</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>30.03684920660667,23.208296316100707,10.91207486556324,6.33144934726556,12.498718881314668,12.498718881314668,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,104.83367089775363,211.7208672086721,992.063492063492,84.8461400097064,134.53011322054329,566.4310313576219,132.68582650001326,222.29335609617297,281.40794020644086,20.32470752745868,20.275750202757504,20.275750202757504,2.7386047750751037,4.201306438250039</t>
+          <t>185.91893564411106,37.05999417551534,531.7157772999103,9.942404472633392,1002.3089011981351,27.652807930069653,5.205287510869865,0.950857908811167,55.05699502514024,74.73759288740052,56.28685516219487,25.681336927982958,502.3734599083459,1897.4059351326184,20.594049190171614,14.970225335394018,13.60448757949489,6.383116418792407,0.7588637617125114,1.773390821727467,0.7727894378409265,188.8800557146276,276.6144513472147,61.78406269881346,27.16895369727391,9.37232127844289,132.8890060450138,1690.9695669890334,310.377527332511,609.5057104179396,362.95874193920497,175.40494493687578,781.9268354027478,615.2339438557633,345.45878335999885,111.64332284907596,82.33720971899993,50.93388340323612,3.6767320203281555,69.28150196219715,630.0052240898638,775.0683454451884,90.73156556812322,3945.769455276097,11506.115769612097,2.571514851901921,10.53738040837284,468.4305341068254,969.7212653390383,29.895167657909404,7.168084894976515,14.178909469921829,56.09618569629844,160.01470455834811,85.59283735760465,14.750250801458101,198.81261109134593,2020.5164465749403,438.77764340452876,12.672889828514315,812.2835604020495,275.7019881478891,10.285280030179644,51.87097222909731,43.506338784569465,27.253642649586418,9.354593450954244,767.6084418768509,9.51180809959626,77.64662015441215,328.5772048907013,610.3502773560309,113.65504367324093,207.91145785709682,163.29708913854276,320.39756326248266,141.7629814797198,24.129782382940586,61.70811403079293,23.311892372872393,27.560843624816385,18.37590426335059,37.24695224235373,51.77398451309847,11.780561281659937,12.00311547776832,9.40122107632549,7.335176023389271,2.7593195988219876,4.302323537710025,20.48682438796216,22.022432104773998,8.450451072453607,20.104267655003277,44.27163558844692,63.98671888351089,6.216898747683834,6.506223100078234,4140.921135617244,1815.910520381487,991.2081796422,1394.3347416119514,543.5866933440042,3289.355741540074,0.7182367379995587,3.611472132972618,18.640002335484397,17.520714341611427,11.702411552040715,5.2174753033656085,8.683185589387488,5.264493111709381,2259.1758219950816,1598.2454514554424</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>27</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-7.228372106978017</v>
+        <v>-3.916155879721605</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>30.03684920660667,23.208296316100707,10.91207486556324,6.33144934726556,12.498718881314668,12.498718881314668,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,104.83367089775363,211.7208672086721,992.063492063492,84.8461400097064,134.53011322054329,566.4310313576219,132.68582650001326,222.29335609617297,281.40794020644086,20.32470752745868,20.275750202757504,20.275750202757504,2.7386047750751037,4.201306438250039</t>
+          <t>13.415689103769846,33.74373292136397,632.2465595866008,2.139012660861899,353.740986484279,6.4561742477988275,11.52709263927734,2.3873205266366337,30.396303542534444,38.55404364525842,2.3734387814540843,7.063001209338603,199.7637333360177,383.984164413266,52.89107086133917,6.456455271693424,88.27320738048729,1.3338340277807088,10.006804279542383,1.255298155672433,1.5076028700195319,209.97649414909142,457.7686803917644,12.199637741798611,26.91871671691011,62.56575941082201,933.1406210520373,1340.2293604546755,512.5963833530345,117.00443554169917,145.42094695727332,383.51378126943683,154.57378154398276,60.591733566251094,140.79444366432136,11.530234320443354,34.327556608084265,132.07735343499695,24.255617244132747,174.70287593137456,474.51133123075607,2541.1736938302797,33.88036889431904,329.0004718609935,829.9156403619762,8.782087693947684,21.659759008878286,700.7229619933605,730.0193974402192,16.22571303129227,3.761215192746245,15.72185942863513,29.28262114823257,69.1354654549312,30.30536124709854,216.00681441391487,108.53691462167956,291.39287724939277,1478.3215029556868,16.22096806878503,3558.226084866097,572.853580383859,27.915041449009255,34.97366375023755,12.165874483265346,28.068702023107328,34.18810662996979,300.990449446867,17.8593991978006,629.1965698507895,386.4661096451041,1556.1548938021958,69.57501976338997,173.55633250338101,192.95074046827847,74.77172974308787,506.8535324796562,13.718126366821096,34.18025632330527,19.830283619191196,11.144294656338756,37.72018292164813,15.90349447435133,58.01608704323714,30.216247653055543,6.4738245907676,17.276556598217038,4.605204407393116,1.4189076832667677,5.177393625747583,45.51686993109715,24.37291585473029,11.922366631262925,33.96622865979403,90.99714986185045,40.9116920853701,23.40698818461901,11.06035424674214,6041.554465488917,2117.7098472864564,322.9885789970949,3228.4124567284925,451.78899851515877,2204.411999516342,0.6873949628126806,3.5442989176844737,12.456297345270004,32.615911168538275,42.9071001566258,3.363506829687889,2.158197834985054,1.100532063354224,1195.9167131201311,654.3170290800426</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-7.228373316170591</v>
+        <v>-4.005648094854555</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30.03684920660667,23.208296316100707,10.91207486556324,6.33144934726556,12.498718881314668,12.498718881314668,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,104.83367089775363,211.7208672086721,992.063492063492,84.8461400097064,134.53011322054329,566.4310313576219,132.68582650001326,222.29335609617297,281.40794020644086,20.32470752745868,20.275750202757504,20.275750202757504,2.7386047750751037,4.201306438250039</t>
+          <t>7.436978855360687,4.371894259671892,224.11413926143135,22.813058768345577,1259.0723653145542,5.3337112681841745,10.530664434516126,5.357026452073837,67.33634536683422,342.26836469756245,66.7737655683802,32.96730607462064,38.07338827688429,875.7593425654549,4.500365090256002,18.476496009580053,75.65494552752969,3.839549493646987,3.079181401494558,0.790352201171378,2.024798869440416,1344.518520893207,173.1299145000716,25.187348911509705,22.045391771665322,9.677975009023642,595.6309079240353,501.11081539492614,155.4066880317305,289.2462915706269,95.00685973452022,187.71750349958822,186.39164195720343,140.7832079940696,121.60041728391232,77.47216256211007,67.09779893676328,220.7760575265515,12.307919641616088,659.3793306017003,468.4859381532996,5316.762408918245,46.83189303592815,945.4833757435295,9907.969764843241,42.10167731436028,28.608212396849808,149.39878597642746,132.3084587888371,215.47199980152348,1.839841803859767,13.514037283954071,133.3528413866772,19.973015859173692,148.0004947459877,306.0660671121429,171.93307579449305,440.23696460461633,199.2807820009854,23.134735661694716,9630.50175405679,60.891043401643955,62.27273267878961,39.25936102956323,20.42524689893036,31.255811914400077,3.0287306046583846,2949.5397481910627,56.73967637914726,320.13354951540674,1942.4049740757214,828.1752606238588,125.0685220985327,413.64231039885783,118.64835162940659,22.9756624782535,459.0862013315201,22.2958108573816,44.918479512924065,112.6087288212819,46.6126035103501,33.14026853533743,26.17650892854269,49.433845986361256,8.576736061247043,1.954342932431521,30.5684486611116,29.52248941723787,6.903391415729254,1.5004892673150216,4.632639613579904,57.943974257409096,21.495700619491096,21.343064823418565,43.10475153701717,56.20080257854684,8.755908013479148,31.932750993758955,2322.458312796687,3784.175347042404,768.8437642745348,2762.777974332579,4564.903918048281,2282.4643775155614,5.180988177189827,2.66293524016935,9.128683203214425,32.455092222452635,101.9230319646484,22.771043837343164,4.828978946304079,17.911859725818402,1247.430003058582,168.58294103545398</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-7.228373316170595</v>
+        <v>-4.259546012007212</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>30.03684920660667,23.208296316100707,10.91207486556324,6.33144934726556,12.498718881314668,12.498718881314668,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,104.83367089775363,211.7208672086721,992.063492063492,84.8461400097064,134.53011322054329,566.4310313576219,132.68582650001326,222.29335609617297,281.40794020644086,20.32470752745868,20.275750202757504,20.275750202757504,2.7386047750751037,4.201306438250039</t>
+          <t>89.8404588109897,35.979219136596846,463.5817620202755,16.66038885636398,687.7463116756728,17.76845930910669,1.6793151640765425,1.5211866752730256,47.86085904835357,420.0492221532522,42.79302225520772,13.9987126763043,335.015866575011,191.39673798926168,3.2545856379844347,2.9284653154245466,26.326128161358007,2.8078475921132995,4.361475725905956,6.894327024958598,5.387703854901929,349.94376728923714,1472.6073951138721,74.19323836613432,5.80087410913684,10.9340207101319,1079.021658765021,47.694445224032926,142.4857142922821,352.3208738874707,201.694246651301,289.168583169345,233.9016883089989,390.31668348694313,729.7379532669762,76.70418747526469,36.5117983326724,83.65965191976099,42.570735575764886,198.21300140556895,429.1731400125652,2037.146310246404,11.489273683725223,1384.2429984916596,959.9037831138012,9.81736279706415,4.817694578895051,180.52088782756343,634.5930627345316,38.329783741797726,7.6882304863350655,3.896007429689655,47.32773970962538,137.99643093954907,24.594667646157422,8.250760265077249,401.6010025960153,1462.3732516378448,310.8836525129179,27.120248267114764,1503.2726427854186,51.88085126373086,119.17495662151988,70.03732771948786,36.51502246971259,21.05644434840454,57.79217939077547,884.1791478344416,64.07317330059676,436.8373835434198,1289.268692956008,1920.7675439851182,115.29202087138765,82.52496151444751,568.4041180626806,86.39476414963337,242.51584350095646,74.41583772916051,21.791524223936683,37.846012275718095,11.166199667544657,35.46772303522661,76.37313601390603,40.70142671574698,27.613176888452607,2.7499381631755053,5.099329392589807,18.964882971642876,4.591426020631046,11.939973410144619,4.533052726576555,43.63575983537779,18.513771394987344,44.95277560234029,47.69833816133309,17.01804639688791,6.463590615135229,63.605440118538475,3220.5581800214795,1969.1077434170575,668.4565237424164,1802.2651012846907,1666.400452656326,1334.6843437043553,5.960657704688191,2.9499128447417764,28.190204441095098,62.07402819397541,15.080228419812476,46.11865812112792,15.089319315647467,16.406726208332138,1599.4598306010034,2311.0723885738707</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-7.228373316170595</v>
+        <v>-4.289481275546581</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>30.03684920660667,23.208296316100707,10.91207486556324,6.33144934726556,12.498718881314668,12.498718881314668,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,104.83367089775363,211.7208672086721,992.063492063492,84.8461400097064,134.53011322054329,566.4310313576219,132.68582650001326,222.29335609617297,281.40794020644086,20.32470752745868,20.275750202757504,20.275750202757504,2.7386047750751037,4.201306438250039</t>
+          <t>26.40414085044968,23.881459033975222,1886.4084541392685,27.361422484223706,250.9146208829244,6.2874520307375334,4.332408436171456,3.2344298365621267,194.59058316541388,28.54419856825747,44.337551781466615,84.56780555206694,331.6240646651785,521.5312307222277,79.58956420095855,3.416823652548252,28.817318698625062,3.896991599303723,17.898633192102768,2.827032935133568,1.154385319204653,588.1537016472424,171.33809110799223,7.495663560144956,43.277191388752414,46.1947814277068,658.3807127899604,240.71787745371532,95.67020682092442,128.59290357049792,331.7466639467656,173.20974923273351,875.4277615999789,1009.0186098763886,123.0831390993492,30.258491696437435,11.725592342156897,72.78306391776542,124.54144995774227,512.4534751848864,206.65045390692677,1297.1987250469947,95.04012550596399,1260.6651386609467,2240.649281937751,10.172937654953607,47.98838778133561,435.3611503874788,331.5194117116274,79.44349346528216,9.941012790007182,3.673059121782072,8.168380355629841,73.48410515353251,105.69158208446768,921.6919770091554,408.7406682693676,2110.7516585742187,534.8719247479127,19.47197128360913,1303.030130159246,104.6147466433163,17.587414602107412,13.851475526599732,36.06661206480801,115.17179487725136,24.24615112327156,380.47503686115243,40.687852522057625,115.94569366066055,1934.904870358087,1948.8483244991767,126.42511177276016,41.77036858665335,35.45674865085193,282.1960579698544,1264.3701905274852,24.233261803045398,17.3031615644622,23.9665814505935,26.609393579524586,12.962771500691261,28.104837175310053,98.27110578472956,18.12857723581923,24.519740858240596,21.019673692264032,5.340708416812227,5.337853909235113,6.966358398367549,15.12384669698422,19.535333590852513,27.128781781293952,38.670243014052396,14.424424562592137,104.4048539653721,28.481031254356218,15.746178296816229,1555.5845218625022,2569.7984797312006,2254.98551995922,4132.977961841336,4546.572714243116,3446.0662249210673,2.485728399790046,9.68762233798948,19.66147855533207,65.6655689763774,62.76312953296159,44.59636817887637,9.040345212602874,18.583532711508145,382.43716991623165,2291.7994985855335</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-7.228373316170595</v>
+        <v>-4.290042922324121</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>30.03684920660667,23.208296316100707,10.91207486556324,6.33144934726556,12.498718881314668,12.498718881314668,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,20.275750202757504,104.83367089775363,211.7208672086721,992.063492063492,84.8461400097064,134.53011322054329,566.4310313576219,132.68582650001326,222.29335609617297,281.40794020644086,20.32470752745868,20.275750202757504,20.275750202757504,2.7386047750751037,4.201306438250039</t>
+          <t>98.27153692407391,11.84000221834333,367.92843705243337,8.211736390934155,895.6447946628521,15.798890345136584,9.72289795239858,4.987951594736515,31.887655294402116,62.28998361924528,9.973858425078854,13.625036941812024,436.8597474495183,2425.599098260515,30.71040005763475,18.215916330283754,59.44758384580256,3.266230527621018,1.6717931761619493,1.8247886155881505,1.2556806369757936,435.4390061406883,502.8907485494805,11.808033469817802,4.7749717464873775,20.863285639724644,187.63200431057987,339.1672057460107,130.8577325125807,94.79545266865097,557.099860255403,196.52613563604814,718.0538471936133,1102.97025802984,334.939232892295,83.03657624230192,22.922375188086157,103.44412844835011,30.609282941181256,536.9830198187235,199.03591961356284,3305.6313603216627,38.84312732470622,2384.7207638810382,3227.4303235046664,32.03964917795187,12.824717440999805,325.2172205169527,536.4196726669729,141.6360942048181,23.815727030783176,1.985624344130402,123.01530450436218,152.524663240823,61.355541090519324,55.36863992167613,155.18063911886725,241.38027154975623,1345.2112528417986,114.29016772410006,872.3405942597678,62.835443010413286,4.054406026728367,7.691327236397056,34.839375889888274,7.692836633714544,27.4134234167906,627.4902599985016,116.7075162584612,45.476666800629474,315.6732549574607,508.43357502419815,131.3711563247865,68.83403602827788,325.26878883673265,390.2664152471962,338.5030264348063,51.25139743652697,24.273702184314928,34.460844243943114,11.484660369597993,13.197271011449356,34.02841687825411,63.78164874113604,19.729321792394796,4.012630503647274,71.39278902858895,5.731563642639228,1.9152411546552943,5.188229273352876,25.099965675452356,23.91143840520952,7.7864775730083435,71.23803468396632,13.54603470469955,13.531197509226262,14.077515291246886,36.6643368861723,1145.7275060012735,1645.8419336645893,979.3925013034957,3022.021597293724,878.7219571153997,1252.3931722895645,1.1291316088901406,1.6899378377646723,35.96296430993581,36.78328363903022,32.00511462172859,49.055433035064794,3.961917403193408,16.545218039907027,326.1947619321293,798.61397927144</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>27</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -1596,7 +3771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1638,7 +3813,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P00944</t>
+          <t>P0AB89</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1650,7 +3825,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P00944</t>
+          <t>P0AB89</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1662,7 +3837,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P00944</t>
+          <t>P0AB89</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1674,7 +3849,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P00944</t>
+          <t>P0AB89</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1686,7 +3861,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P0ABI8_P0ABJ1_P0ABJ3_P0ABJ6</t>
+          <t>P0AD61</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1698,7 +3873,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P0AGD3</t>
+          <t>P0AD61</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1710,7 +3885,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P60844</t>
+          <t>P00864</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1722,7 +3897,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P60844</t>
+          <t>P00864</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1734,7 +3909,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P0A754</t>
+          <t>P0A825</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1746,7 +3921,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P0A754</t>
+          <t>P0A825</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1758,7 +3933,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P0A754</t>
+          <t>P0A825</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1770,7 +3945,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P00509</t>
+          <t>P0A825</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1782,7 +3957,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P00509</t>
+          <t>P0A825</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1794,7 +3969,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P00509</t>
+          <t>P0A825</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1806,7 +3981,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P00509</t>
+          <t>P0A825</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1818,7 +3993,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P00509</t>
+          <t>P0A9M8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1830,7 +4005,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P00509</t>
+          <t>P0A9M8</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1842,7 +4017,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P00509</t>
+          <t>P0A9M8</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1854,7 +4029,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P00509</t>
+          <t>P0A9M8</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1866,7 +4041,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P0A6A3</t>
+          <t>P05793</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1878,7 +4053,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P0A6A3</t>
+          <t>P05793</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1890,7 +4065,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P0AEP1</t>
+          <t>P05793</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1902,7 +4077,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>P0AEP1</t>
+          <t>P05793</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1914,7 +4089,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>P06959_P0A9P0_P0AFG8</t>
+          <t>P75804</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1926,10 +4101,1054 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>P23721</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>P23721</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>P23721</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>P23721</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>P15639</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>P15639</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>P15639</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>P15639</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>P0AGB0</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>P00562</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>P00562</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>P00562</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>P00562</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>P37306</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>P37306</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>P06989</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>P06989</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>P06989</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>P06989</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>P00370</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>P00370</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>P0A6C5</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>P0A6C5</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>P25516</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>P25516</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>P25516</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>P25516</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>P0A6A8_P0AAI9</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>P0A6A8_P0AAI9</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>P13009</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>P13009</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>P0A6K1</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>P0A6K1</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>P07001_P0AB67</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>P15640</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>P15640</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>P0AC98</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>P0AC98</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>P0AC98</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>P0AEP1</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>P0AEP1</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>P0A6A3</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>P0A6A3</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>P00509</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>P00509</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>P00509</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>P00509</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>P00509</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>P00509</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>P00509</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>P00509</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>P0A754</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>P0A754</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>P0A754</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>P60844</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>P60844</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>P0AGD3</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>P0ABI8_P0ABJ1_P0ABJ3_P0ABJ6</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>P00944</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>P00944</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>P00944</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>P00944</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
           <t>P06959_P0A9P0_P0AFG8</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>P06959_P0A9P0_P0AFG8</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>P0A9B2</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>P0A9B2</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>P0A9B2</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>P0A9B2</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>P0A9B2</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>P0A9B2</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>P0ADU2</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>P0ADU2</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>P0AB80</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>P0AB80</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>P0AB80</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>P0AB80</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>P0AB80</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>P0AB80</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>P62707</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>P62707</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>P78055</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>P78055</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>P26458_P26459</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>P26458_P26459</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>P0A799</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>P0A799</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>P60757</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>P60757</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
         <is>
           <t>mutation</t>
         </is>
